--- a/dbm-ui/backend/ticket/exclusive_ticket.xlsx
+++ b/dbm-ui/backend/ticket/exclusive_ticket.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760" firstSheet="4" activeTab="7"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="cluster_mysql_exclusive" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="101">
   <si>
     <t>能否并行</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>MySQL 集群授权</t>
+  </si>
+  <si>
+    <t>MySQL 迁移升级</t>
   </si>
   <si>
     <t>Y</t>
@@ -347,7 +350,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -410,13 +413,6 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="SimSun"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1144,28 +1140,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1174,118 +1173,115 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1419,14 +1415,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1748,7 +1744,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T201"/>
+  <dimension ref="A1:U201"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1770,7 +1766,7 @@
     <col min="20" max="20" width="11.3035714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.75" customHeight="1" spans="1:20">
+    <row r="1" ht="36.75" customHeight="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1831,1205 +1827,1309 @@
       <c r="T1" s="40" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" ht="36.75" customHeight="1" spans="1:20">
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" ht="36.75" customHeight="1" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" ht="36.75" customHeight="1" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="36.75" customHeight="1" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="36.75" customHeight="1" spans="1:21">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="36.75" customHeight="1" spans="1:21">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="36.75" customHeight="1" spans="1:21">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" ht="36.75" customHeight="1" spans="1:21">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="36.75" customHeight="1" spans="1:21">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" ht="36.75" customHeight="1" spans="1:21">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" ht="36.75" customHeight="1" spans="1:21">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" ht="36.75" customHeight="1" spans="1:21">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="36.75" customHeight="1" spans="1:21">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U13" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" ht="36.75" customHeight="1" spans="1:21">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" ht="36.75" customHeight="1" spans="1:21">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" ht="36.75" customHeight="1" spans="1:21">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" ht="36.75" customHeight="1" spans="1:20">
+        <v>22</v>
+      </c>
+      <c r="U16" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" ht="36.75" customHeight="1" spans="1:21">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" ht="36.75" customHeight="1" spans="1:21">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" ht="36.75" customHeight="1" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" ht="36.75" customHeight="1" spans="1:21">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" ht="36.75" spans="1:20">
+        <v>21</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" ht="36.75" spans="1:21">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M20" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P20" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="42" t="s">
+        <v>21</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:21">
+      <c r="A21" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P20" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S20" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
-      <c r="A21" s="43"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="44"/>
-      <c r="Q21" s="44"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
+      <c r="B21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="M21" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="O21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="P21" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="R21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="S21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="T21" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="U21" s="43" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="22" ht="17.6" spans="1:19">
       <c r="A22" s="44"/>
@@ -6836,1495 +6936,1495 @@
         <v>0</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="39" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="39" t="s">
-        <v>24</v>
-      </c>
       <c r="K1" s="39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L1" s="39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M1" s="39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N1" s="39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O1" s="39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P1" s="39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q1" s="39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R1" s="39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S1" s="39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T1" s="39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U1" s="39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V1" s="39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="36.75" spans="1:22">
       <c r="A2" s="40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="36.75" spans="1:22">
       <c r="A3" s="40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="53.75" spans="1:22">
       <c r="A4" s="40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:22">
       <c r="A5" s="40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="36.75" spans="1:22">
       <c r="A6" s="40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P6" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q6" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V6" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="36.75" spans="1:22">
       <c r="A7" s="40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R7" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="36.75" spans="1:22">
       <c r="A8" s="40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N8" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P8" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R8" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V8" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" ht="36.75" spans="1:22">
       <c r="A9" s="40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R9" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V9" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" ht="53.75" spans="1:22">
       <c r="A10" s="40" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="55" customHeight="1" spans="1:22">
       <c r="A11" s="40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R11" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V11" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="61" customHeight="1" spans="1:22">
       <c r="A12" s="40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R12" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V12" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:22">
       <c r="A13" s="40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U13" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="36.75" spans="1:22">
       <c r="A14" s="40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T14" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="36.75" spans="1:22">
       <c r="A15" s="40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="53.75" spans="1:22">
       <c r="A16" s="40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H16" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I16" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T16" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V16" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" ht="53.75" spans="1:22">
       <c r="A17" s="40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V17" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" ht="53.75" spans="1:22">
       <c r="A18" s="40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H18" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L18" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S18" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V18" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" ht="53.75" spans="1:22">
       <c r="A19" s="40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N19" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R19" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V19" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" ht="53.75" spans="1:22">
       <c r="A20" s="40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N20" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U20" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V20" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" ht="53.75" spans="1:22">
       <c r="A21" s="40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T21" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" ht="53.75" spans="1:22">
       <c r="A22" s="40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T22" s="41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -8347,119 +8447,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" ht="36.75" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="36.75" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="36.75" customHeight="1" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="36.75" customHeight="1" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="36.75" customHeight="1" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -8479,119 +8579,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" ht="36.75" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="36.75" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="36.75" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="36.75" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -8611,119 +8711,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" ht="36.75" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="36.75" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="36.75" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="36.75" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -8743,119 +8843,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" ht="36.75" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="36.75" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="36.75" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="36.75" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -8875,119 +8975,119 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" ht="36.75" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="36.75" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="36.75" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="36.75" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -9022,1239 +9122,1239 @@
         <v>0</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D1" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F1" s="25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G1" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H1" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I1" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K1" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L1" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M1" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N1" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O1" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P1" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q1" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R1" s="25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="S1" s="24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T1" s="24" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" ht="36.75" spans="1:20">
       <c r="A2" s="25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N2" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S2" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T2" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="36.75" spans="1:20">
       <c r="A3" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M3" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R3" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S3" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T3" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" ht="36.75" spans="1:20">
       <c r="A4" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R4" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S4" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T4" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="36.75" spans="1:20">
       <c r="A5" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q5" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S5" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T5" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="35.05" customHeight="1" spans="1:20">
       <c r="A6" s="25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q6" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R6" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S6" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T6" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="36.75" spans="1:20">
       <c r="A7" s="24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R7" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S7" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T7" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" ht="36.75" spans="1:20">
       <c r="A8" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N8" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R8" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S8" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T8" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" ht="36.75" spans="1:20">
       <c r="A9" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O9" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R9" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S9" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T9" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" ht="36.75" spans="1:20">
       <c r="A10" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M10" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P10" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q10" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S10" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T10" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" ht="36.75" spans="1:20">
       <c r="A11" s="25" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M11" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N11" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P11" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q11" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R11" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S11" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T11" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" ht="36.75" spans="1:20">
       <c r="A12" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J12" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M12" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q12" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R12" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S12" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T12" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" ht="50.05" customHeight="1" spans="1:20">
       <c r="A13" s="24" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R13" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S13" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T13" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1" spans="1:20">
       <c r="A14" s="25" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N14" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R14" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S14" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T14" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" ht="36.75" spans="1:20">
       <c r="A15" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O15" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R15" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S15" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T15" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" ht="36.75" spans="1:20">
       <c r="A16" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K16" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M16" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P16" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R16" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S16" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T16" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" ht="36.75" spans="1:20">
       <c r="A17" s="25" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J17" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K17" s="29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M17" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q17" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R17" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S17" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T17" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" ht="36.75" spans="1:20">
       <c r="A18" s="25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K18" s="27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L18" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q18" s="28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R18" s="26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S18" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T18" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" ht="36.75" spans="1:20">
       <c r="A19" s="24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K19" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M19" s="33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R19" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S19" s="32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T19" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" ht="29" customHeight="1" spans="1:20">
       <c r="A20" s="30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R20" s="32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S20" s="30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T20" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -10274,704 +10374,704 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" ht="71.75" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" ht="53.75" spans="1:15">
       <c r="A3" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="53.75" spans="1:15">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" ht="53.75" spans="1:15">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="53.75" spans="1:15">
       <c r="A6" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="53.75" spans="1:15">
       <c r="A7" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="53.75" spans="1:15">
       <c r="A8" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="53.75" spans="1:15">
       <c r="A9" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" ht="71.75" spans="1:15">
       <c r="A10" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="53.75" spans="1:15">
       <c r="A11" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="53.75" spans="1:15">
       <c r="A12" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" ht="36.75" spans="1:15">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" ht="53.75" spans="1:15">
       <c r="A14" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="53.75" spans="1:15">
       <c r="A15" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dbm-ui/backend/ticket/exclusive_ticket.xlsx
+++ b/dbm-ui/backend/ticket/exclusive_ticket.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowWidth="28000" windowHeight="14500"/>
   </bookViews>
   <sheets>
     <sheet name="cluster_mysql_exclusive" sheetId="1" r:id="rId1"/>
@@ -1285,7 +1285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1424,6 +1424,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1744,7 +1750,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U201"/>
+  <dimension ref="A1:V201"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1827,11 +1833,11 @@
       <c r="T1" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="40" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" ht="36.75" customHeight="1" spans="1:21">
+    <row r="2" ht="36.75" customHeight="1" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1892,11 +1898,12 @@
       <c r="T2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" ht="36.75" customHeight="1" spans="1:21">
+      <c r="U2" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="48"/>
+    </row>
+    <row r="3" ht="36.75" customHeight="1" spans="1:22">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1957,11 +1964,12 @@
       <c r="T3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="U3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" ht="36.75" customHeight="1" spans="1:21">
+      <c r="U3" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="V3" s="48"/>
+    </row>
+    <row r="4" ht="36.75" customHeight="1" spans="1:22">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -2022,11 +2030,12 @@
       <c r="T4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="U4" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="36.75" customHeight="1" spans="1:21">
+      <c r="U4" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="V4" s="48"/>
+    </row>
+    <row r="5" ht="36.75" customHeight="1" spans="1:22">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -2090,8 +2099,9 @@
       <c r="U5" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V5" s="48"/>
+    </row>
+    <row r="6" ht="36.75" customHeight="1" spans="1:22">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -2155,8 +2165,9 @@
       <c r="U6" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V6" s="48"/>
+    </row>
+    <row r="7" ht="36.75" customHeight="1" spans="1:22">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -2220,8 +2231,9 @@
       <c r="U7" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V7" s="48"/>
+    </row>
+    <row r="8" ht="36.75" customHeight="1" spans="1:22">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -2285,8 +2297,9 @@
       <c r="U8" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V8" s="48"/>
+    </row>
+    <row r="9" ht="36.75" customHeight="1" spans="1:22">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -2350,8 +2363,9 @@
       <c r="U9" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V9" s="48"/>
+    </row>
+    <row r="10" ht="36.75" customHeight="1" spans="1:22">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -2415,8 +2429,9 @@
       <c r="U10" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V10" s="48"/>
+    </row>
+    <row r="11" ht="36.75" customHeight="1" spans="1:22">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -2480,8 +2495,9 @@
       <c r="U11" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V11" s="48"/>
+    </row>
+    <row r="12" ht="36.75" customHeight="1" spans="1:22">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -2545,8 +2561,9 @@
       <c r="U12" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V12" s="48"/>
+    </row>
+    <row r="13" ht="36.75" customHeight="1" spans="1:22">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -2610,8 +2627,9 @@
       <c r="U13" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V13" s="48"/>
+    </row>
+    <row r="14" ht="36.75" customHeight="1" spans="1:22">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -2675,8 +2693,9 @@
       <c r="U14" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V14" s="48"/>
+    </row>
+    <row r="15" ht="36.75" customHeight="1" spans="1:22">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -2740,8 +2759,9 @@
       <c r="U15" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" ht="36.75" customHeight="1" spans="1:21">
+      <c r="V15" s="48"/>
+    </row>
+    <row r="16" ht="36.75" customHeight="1" spans="1:22">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -2805,6 +2825,7 @@
       <c r="U16" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="V16" s="48"/>
     </row>
     <row r="17" ht="36.75" customHeight="1" spans="1:21">
       <c r="A17" s="1" t="s">
@@ -3067,7 +3088,7 @@
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:21">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="43" t="s">

--- a/dbm-ui/backend/ticket/exclusive_ticket.xlsx
+++ b/dbm-ui/backend/ticket/exclusive_ticket.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10905"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevnzheng/Projects/blueking-dbm/dbm-ui/backend/ticket/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4421548-4D1C-D241-9785-881F680D53C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cluster_mysql_exclusive" sheetId="1" r:id="rId1"/>
@@ -35,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5045" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5094" uniqueCount="156">
   <si>
     <t>能否并行</t>
   </si>
@@ -501,22 +507,19 @@
   <si>
     <t>SQLServer 集群授权</t>
   </si>
+  <si>
+    <t>Redis 容灾演练</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -536,7 +539,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -582,163 +585,12 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -757,194 +609,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="19">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1080,251 +746,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1439,61 +863,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1751,40 +1131,40 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU201"/>
-  <sheetFormatPr defaultColWidth="9.66071428571429" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.1607142857143" customWidth="1"/>
-    <col min="2" max="2" width="11.1607142857143" customWidth="1"/>
+    <col min="1" max="1" width="21.1640625" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" customWidth="1"/>
     <col min="3" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="10.3303571428571" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="7.66071428571429" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="13.3303571428571" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
     <col min="10" max="11" width="9.5" customWidth="1"/>
-    <col min="12" max="13" width="7.66071428571429" customWidth="1"/>
-    <col min="14" max="15" width="10.3303571428571" customWidth="1"/>
-    <col min="16" max="16" width="10.1607142857143" customWidth="1"/>
-    <col min="17" max="18" width="10.3303571428571" customWidth="1"/>
-    <col min="19" max="19" width="7.66071428571429" customWidth="1"/>
-    <col min="20" max="21" width="9.66071428571429" customWidth="1"/>
+    <col min="12" max="13" width="7.6640625" customWidth="1"/>
+    <col min="14" max="15" width="10.33203125" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="18" width="10.33203125" customWidth="1"/>
+    <col min="19" max="19" width="7.6640625" customWidth="1"/>
+    <col min="20" max="21" width="9.6640625" customWidth="1"/>
     <col min="22" max="30" width="9.5" customWidth="1"/>
-    <col min="31" max="31" width="7.66071428571429" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" customWidth="1"/>
     <col min="32" max="32" width="9.5" customWidth="1"/>
     <col min="33" max="33" width="12.5" customWidth="1"/>
-    <col min="34" max="34" width="13.6607142857143" customWidth="1"/>
+    <col min="34" max="34" width="13.6640625" customWidth="1"/>
     <col min="35" max="38" width="12.5" customWidth="1"/>
-    <col min="39" max="40" width="14.6607142857143" customWidth="1"/>
+    <col min="39" max="40" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="71" spans="1:47">
+    <row r="1" spans="1:47" ht="64">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1927,7 +1307,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" ht="18" spans="1:47">
+    <row r="2" spans="1:47" ht="16">
       <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
@@ -2070,7 +1450,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="36" spans="1:47">
+    <row r="3" spans="1:47" ht="32">
       <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
@@ -2213,7 +1593,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="36" spans="1:47">
+    <row r="4" spans="1:47" ht="32">
       <c r="A4" s="31" t="s">
         <v>3</v>
       </c>
@@ -2356,7 +1736,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="18" spans="1:47">
+    <row r="5" spans="1:47" ht="16">
       <c r="A5" s="31" t="s">
         <v>6</v>
       </c>
@@ -2499,7 +1879,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="36" spans="1:47">
+    <row r="6" spans="1:47" ht="32">
       <c r="A6" s="31" t="s">
         <v>5</v>
       </c>
@@ -2642,7 +2022,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="18" spans="1:47">
+    <row r="7" spans="1:47" ht="16">
       <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
@@ -2785,7 +2165,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" ht="18" spans="1:47">
+    <row r="8" spans="1:47" ht="16">
       <c r="A8" s="31" t="s">
         <v>7</v>
       </c>
@@ -2928,7 +2308,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="18" spans="1:47">
+    <row r="9" spans="1:47" ht="16">
       <c r="A9" s="31" t="s">
         <v>8</v>
       </c>
@@ -3071,7 +2451,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" ht="18" spans="1:47">
+    <row r="10" spans="1:47" ht="16">
       <c r="A10" s="31" t="s">
         <v>9</v>
       </c>
@@ -3214,7 +2594,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="18" spans="1:47">
+    <row r="11" spans="1:47" ht="16">
       <c r="A11" s="31" t="s">
         <v>10</v>
       </c>
@@ -3357,7 +2737,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="18" spans="1:47">
+    <row r="12" spans="1:47" ht="16">
       <c r="A12" s="31" t="s">
         <v>11</v>
       </c>
@@ -3500,7 +2880,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" ht="18" spans="1:47">
+    <row r="13" spans="1:47" ht="16">
       <c r="A13" s="31" t="s">
         <v>12</v>
       </c>
@@ -3643,7 +3023,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="18" spans="1:47">
+    <row r="14" spans="1:47" ht="16">
       <c r="A14" s="31" t="s">
         <v>13</v>
       </c>
@@ -3786,7 +3166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" ht="18" spans="1:47">
+    <row r="15" spans="1:47" ht="16">
       <c r="A15" s="31" t="s">
         <v>14</v>
       </c>
@@ -3929,7 +3309,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="36" spans="1:47">
+    <row r="16" spans="1:47" ht="32">
       <c r="A16" s="31" t="s">
         <v>15</v>
       </c>
@@ -4072,7 +3452,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="18" spans="1:47">
+    <row r="17" spans="1:47" ht="16">
       <c r="A17" s="31" t="s">
         <v>16</v>
       </c>
@@ -4215,7 +3595,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="18" spans="1:47">
+    <row r="18" spans="1:47" ht="16">
       <c r="A18" s="31" t="s">
         <v>17</v>
       </c>
@@ -4358,7 +3738,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" ht="18" spans="1:47">
+    <row r="19" spans="1:47" ht="16">
       <c r="A19" s="31" t="s">
         <v>18</v>
       </c>
@@ -4501,7 +3881,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" ht="18" spans="1:47">
+    <row r="20" spans="1:47" ht="16">
       <c r="A20" s="31" t="s">
         <v>19</v>
       </c>
@@ -4644,7 +4024,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" ht="18" spans="1:47">
+    <row r="21" spans="1:47" ht="16">
       <c r="A21" s="31" t="s">
         <v>20</v>
       </c>
@@ -4787,7 +4167,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" ht="18" spans="1:47">
+    <row r="22" spans="1:47" ht="16">
       <c r="A22" s="31" t="s">
         <v>21</v>
       </c>
@@ -4930,7 +4310,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" ht="18" spans="1:47">
+    <row r="23" spans="1:47" ht="16">
       <c r="A23" s="31" t="s">
         <v>22</v>
       </c>
@@ -5073,7 +4453,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="36" spans="1:47">
+    <row r="24" spans="1:47" ht="16">
       <c r="A24" s="31" t="s">
         <v>23</v>
       </c>
@@ -5216,7 +4596,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" ht="18" spans="1:47">
+    <row r="25" spans="1:47" ht="16">
       <c r="A25" s="31" t="s">
         <v>24</v>
       </c>
@@ -5359,7 +4739,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" ht="18" spans="1:47">
+    <row r="26" spans="1:47" ht="16">
       <c r="A26" s="31" t="s">
         <v>25</v>
       </c>
@@ -5502,7 +4882,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" ht="36" spans="1:47">
+    <row r="27" spans="1:47" ht="32">
       <c r="A27" s="31" t="s">
         <v>26</v>
       </c>
@@ -5645,7 +5025,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" ht="36" spans="1:47">
+    <row r="28" spans="1:47" ht="32">
       <c r="A28" s="31" t="s">
         <v>27</v>
       </c>
@@ -5788,7 +5168,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" ht="36" spans="1:47">
+    <row r="29" spans="1:47" ht="32">
       <c r="A29" s="31" t="s">
         <v>28</v>
       </c>
@@ -5931,7 +5311,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" ht="36" spans="1:47">
+    <row r="30" spans="1:47" ht="32">
       <c r="A30" s="31" t="s">
         <v>29</v>
       </c>
@@ -6074,7 +5454,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" ht="18" spans="1:47">
+    <row r="31" spans="1:47" ht="16">
       <c r="A31" s="31" t="s">
         <v>30</v>
       </c>
@@ -6217,7 +5597,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" ht="18" spans="1:47">
+    <row r="32" spans="1:47" ht="16">
       <c r="A32" s="31" t="s">
         <v>31</v>
       </c>
@@ -6360,7 +5740,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" ht="18" spans="1:47">
+    <row r="33" spans="1:47" ht="16">
       <c r="A33" s="31" t="s">
         <v>32</v>
       </c>
@@ -6503,7 +5883,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="18" spans="1:47">
+    <row r="34" spans="1:47" ht="16">
       <c r="A34" s="31" t="s">
         <v>33</v>
       </c>
@@ -6646,7 +6026,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" ht="18" spans="1:47">
+    <row r="35" spans="1:47" ht="16">
       <c r="A35" s="31" t="s">
         <v>34</v>
       </c>
@@ -6789,7 +6169,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" ht="18" spans="1:47">
+    <row r="36" spans="1:47" ht="16">
       <c r="A36" s="31" t="s">
         <v>35</v>
       </c>
@@ -6932,7 +6312,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" ht="18" spans="1:47">
+    <row r="37" spans="1:47" ht="16">
       <c r="A37" s="31" t="s">
         <v>36</v>
       </c>
@@ -7075,7 +6455,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" ht="36" spans="1:47">
+    <row r="38" spans="1:47" ht="16">
       <c r="A38" s="31" t="s">
         <v>37</v>
       </c>
@@ -7218,7 +6598,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" ht="18" spans="1:47">
+    <row r="39" spans="1:47" ht="16">
       <c r="A39" s="31" t="s">
         <v>38</v>
       </c>
@@ -7361,7 +6741,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" ht="18" spans="1:47">
+    <row r="40" spans="1:47" ht="16">
       <c r="A40" s="31" t="s">
         <v>39</v>
       </c>
@@ -7504,7 +6884,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" ht="18" spans="1:47">
+    <row r="41" spans="1:47" ht="16">
       <c r="A41" s="31" t="s">
         <v>40</v>
       </c>
@@ -7647,7 +7027,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" ht="18" spans="1:47">
+    <row r="42" spans="1:47" ht="16">
       <c r="A42" s="31" t="s">
         <v>41</v>
       </c>
@@ -7790,7 +7170,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" ht="18" spans="1:47">
+    <row r="43" spans="1:47" ht="16">
       <c r="A43" s="31" t="s">
         <v>42</v>
       </c>
@@ -7933,7 +7313,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" ht="18" spans="1:47">
+    <row r="44" spans="1:47" ht="16">
       <c r="A44" s="31" t="s">
         <v>43</v>
       </c>
@@ -8076,7 +7456,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" ht="18" spans="1:47">
+    <row r="45" spans="1:47" ht="16">
       <c r="A45" s="31" t="s">
         <v>44</v>
       </c>
@@ -8219,7 +7599,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" ht="36" spans="1:47">
+    <row r="46" spans="1:47" ht="32">
       <c r="A46" s="31" t="s">
         <v>45</v>
       </c>
@@ -8362,7 +7742,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" ht="36" spans="1:47">
+    <row r="47" spans="1:47" ht="32">
       <c r="A47" s="31" t="s">
         <v>46</v>
       </c>
@@ -8505,7 +7885,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:47">
       <c r="A48" s="35"/>
       <c r="B48" s="35"/>
       <c r="C48" s="35"/>
@@ -11741,33 +11121,31 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AO41"/>
-  <sheetFormatPr defaultColWidth="10.6607142857143" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.8303571428571" customWidth="1"/>
-    <col min="2" max="5" width="14.1607142857143" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="5" width="14.1640625" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="11" width="14.1607142857143" customWidth="1"/>
+    <col min="7" max="11" width="14.1640625" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="18" width="14.1607142857143" customWidth="1"/>
+    <col min="14" max="18" width="14.1640625" customWidth="1"/>
     <col min="19" max="19" width="19" customWidth="1"/>
-    <col min="20" max="21" width="9.66071428571429" customWidth="1"/>
-    <col min="22" max="24" width="9.83035714285714" customWidth="1"/>
-    <col min="25" max="25" width="10.6607142857143" customWidth="1"/>
-    <col min="26" max="31" width="9.83035714285714" customWidth="1"/>
-    <col min="32" max="32" width="10.1607142857143" customWidth="1"/>
-    <col min="33" max="35" width="9.83035714285714" customWidth="1"/>
+    <col min="20" max="21" width="9.6640625" customWidth="1"/>
+    <col min="22" max="24" width="9.83203125" customWidth="1"/>
+    <col min="25" max="25" width="10.6640625" customWidth="1"/>
+    <col min="26" max="31" width="9.83203125" customWidth="1"/>
+    <col min="32" max="32" width="10.1640625" customWidth="1"/>
+    <col min="33" max="35" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="71" spans="1:41">
+    <row r="1" spans="1:41" ht="64">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -11892,7 +11270,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" ht="36" spans="1:41">
+    <row r="2" spans="1:41" ht="32">
       <c r="A2" s="21" t="s">
         <v>49</v>
       </c>
@@ -12017,7 +11395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="36" spans="1:41">
+    <row r="3" spans="1:41" ht="32">
       <c r="A3" s="21" t="s">
         <v>50</v>
       </c>
@@ -12142,7 +11520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="36" spans="1:41">
+    <row r="4" spans="1:41" ht="32">
       <c r="A4" s="21" t="s">
         <v>51</v>
       </c>
@@ -12267,7 +11645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="18" spans="1:41">
+    <row r="5" spans="1:41" ht="16">
       <c r="A5" s="21" t="s">
         <v>52</v>
       </c>
@@ -12392,7 +11770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="18" spans="1:41">
+    <row r="6" spans="1:41" ht="16">
       <c r="A6" s="21" t="s">
         <v>53</v>
       </c>
@@ -12517,7 +11895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="36" spans="1:41">
+    <row r="7" spans="1:41" ht="32">
       <c r="A7" s="21" t="s">
         <v>54</v>
       </c>
@@ -12642,7 +12020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" ht="36" spans="1:41">
+    <row r="8" spans="1:41" ht="32">
       <c r="A8" s="21" t="s">
         <v>55</v>
       </c>
@@ -12767,7 +12145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="36" spans="1:41">
+    <row r="9" spans="1:41" ht="32">
       <c r="A9" s="21" t="s">
         <v>56</v>
       </c>
@@ -12892,7 +12270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" ht="18" spans="1:41">
+    <row r="10" spans="1:41" ht="16">
       <c r="A10" s="21" t="s">
         <v>57</v>
       </c>
@@ -13017,7 +12395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="36" spans="1:41">
+    <row r="11" spans="1:41" ht="32">
       <c r="A11" s="21" t="s">
         <v>58</v>
       </c>
@@ -13142,7 +12520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="36" spans="1:41">
+    <row r="12" spans="1:41" ht="32">
       <c r="A12" s="21" t="s">
         <v>59</v>
       </c>
@@ -13267,7 +12645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" ht="36" spans="1:41">
+    <row r="13" spans="1:41" ht="32">
       <c r="A13" s="21" t="s">
         <v>60</v>
       </c>
@@ -13392,7 +12770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="36" spans="1:41">
+    <row r="14" spans="1:41" ht="32">
       <c r="A14" s="21" t="s">
         <v>61</v>
       </c>
@@ -13517,7 +12895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" ht="36" spans="1:41">
+    <row r="15" spans="1:41" ht="32">
       <c r="A15" s="21" t="s">
         <v>62</v>
       </c>
@@ -13642,7 +13020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="36" spans="1:41">
+    <row r="16" spans="1:41" ht="32">
       <c r="A16" s="21" t="s">
         <v>63</v>
       </c>
@@ -13767,7 +13145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="36" spans="1:41">
+    <row r="17" spans="1:41" ht="32">
       <c r="A17" s="21" t="s">
         <v>64</v>
       </c>
@@ -13892,7 +13270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="36" spans="1:41">
+    <row r="18" spans="1:41" ht="32">
       <c r="A18" s="21" t="s">
         <v>65</v>
       </c>
@@ -14017,7 +13395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" ht="36" spans="1:41">
+    <row r="19" spans="1:41" ht="32">
       <c r="A19" s="21" t="s">
         <v>66</v>
       </c>
@@ -14142,7 +13520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" ht="36" spans="1:41">
+    <row r="20" spans="1:41" ht="32">
       <c r="A20" s="21" t="s">
         <v>67</v>
       </c>
@@ -14267,7 +13645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" ht="36" spans="1:41">
+    <row r="21" spans="1:41" ht="32">
       <c r="A21" s="21" t="s">
         <v>68</v>
       </c>
@@ -14392,7 +13770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" ht="36" spans="1:41">
+    <row r="22" spans="1:41" ht="32">
       <c r="A22" s="21" t="s">
         <v>69</v>
       </c>
@@ -14517,7 +13895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" ht="36" spans="1:41">
+    <row r="23" spans="1:41" ht="32">
       <c r="A23" s="21" t="s">
         <v>70</v>
       </c>
@@ -14642,7 +14020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="36" spans="1:41">
+    <row r="24" spans="1:41" ht="32">
       <c r="A24" s="21" t="s">
         <v>71</v>
       </c>
@@ -14767,7 +14145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" ht="36" spans="1:41">
+    <row r="25" spans="1:41" ht="32">
       <c r="A25" s="21" t="s">
         <v>72</v>
       </c>
@@ -14892,7 +14270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" ht="36" spans="1:41">
+    <row r="26" spans="1:41" ht="32">
       <c r="A26" s="21" t="s">
         <v>73</v>
       </c>
@@ -15017,7 +14395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" ht="36" spans="1:41">
+    <row r="27" spans="1:41" ht="32">
       <c r="A27" s="21" t="s">
         <v>74</v>
       </c>
@@ -15142,7 +14520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" ht="36" spans="1:41">
+    <row r="28" spans="1:41" ht="32">
       <c r="A28" s="21" t="s">
         <v>75</v>
       </c>
@@ -15267,7 +14645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" ht="36" spans="1:41">
+    <row r="29" spans="1:41" ht="32">
       <c r="A29" s="21" t="s">
         <v>76</v>
       </c>
@@ -15392,7 +14770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" ht="36" spans="1:41">
+    <row r="30" spans="1:41" ht="32">
       <c r="A30" s="21" t="s">
         <v>77</v>
       </c>
@@ -15517,7 +14895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" ht="18" spans="1:41">
+    <row r="31" spans="1:41" ht="16">
       <c r="A31" s="21" t="s">
         <v>78</v>
       </c>
@@ -15642,7 +15020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" ht="36" spans="1:41">
+    <row r="32" spans="1:41" ht="32">
       <c r="A32" s="21" t="s">
         <v>79</v>
       </c>
@@ -15765,7 +15143,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" ht="36" spans="1:41">
+    <row r="33" spans="1:41" ht="32">
       <c r="A33" s="21" t="s">
         <v>80</v>
       </c>
@@ -15890,7 +15268,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="36" spans="1:41">
+    <row r="34" spans="1:41" ht="32">
       <c r="A34" s="21" t="s">
         <v>81</v>
       </c>
@@ -16015,7 +15393,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" ht="36" spans="1:41">
+    <row r="35" spans="1:41" ht="32">
       <c r="A35" s="21" t="s">
         <v>82</v>
       </c>
@@ -16140,7 +15518,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" ht="36" spans="1:41">
+    <row r="36" spans="1:41" ht="32">
       <c r="A36" s="21" t="s">
         <v>83</v>
       </c>
@@ -16265,7 +15643,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" ht="36" spans="1:41">
+    <row r="37" spans="1:41" ht="32">
       <c r="A37" s="21" t="s">
         <v>84</v>
       </c>
@@ -16390,7 +15768,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" ht="36" spans="1:41">
+    <row r="38" spans="1:41" ht="32">
       <c r="A38" s="21" t="s">
         <v>85</v>
       </c>
@@ -16515,7 +15893,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" ht="36" spans="1:41">
+    <row r="39" spans="1:41" ht="32">
       <c r="A39" s="21" t="s">
         <v>86</v>
       </c>
@@ -16640,7 +16018,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" ht="36" spans="1:41">
+    <row r="40" spans="1:41" ht="32">
       <c r="A40" s="21" t="s">
         <v>87</v>
       </c>
@@ -16765,7 +16143,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" ht="36" spans="1:41">
+    <row r="41" spans="1:41" ht="32">
       <c r="A41" s="21" t="s">
         <v>88</v>
       </c>
@@ -16892,25 +16270,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultColWidth="9.16071428571429" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Y25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="10" max="10" width="8.66071428571429" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="9.33035714285714" customWidth="1"/>
-    <col min="14" max="15" width="10.6607142857143" customWidth="1"/>
-    <col min="16" max="21" width="9.66071428571429" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" customWidth="1"/>
+    <col min="14" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="21" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="71.75" spans="1:24">
+    <row r="1" spans="1:25" ht="49" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16983,8 +16359,11 @@
       <c r="X1" s="16" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="2" ht="36.75" spans="1:24">
+      <c r="Y1" s="16" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="33" thickBot="1">
       <c r="A2" s="10" t="s">
         <v>89</v>
       </c>
@@ -17057,8 +16436,11 @@
       <c r="X2" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" ht="36.75" spans="1:24">
+      <c r="Y2" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="33" thickBot="1">
       <c r="A3" s="10" t="s">
         <v>90</v>
       </c>
@@ -17131,8 +16513,11 @@
       <c r="X3" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" ht="53.75" spans="1:24">
+      <c r="Y3" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="49" thickBot="1">
       <c r="A4" s="10" t="s">
         <v>91</v>
       </c>
@@ -17205,8 +16590,11 @@
       <c r="X4" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" ht="36.75" spans="1:24">
+      <c r="Y4" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="33" thickBot="1">
       <c r="A5" s="10" t="s">
         <v>92</v>
       </c>
@@ -17279,8 +16667,11 @@
       <c r="X5" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" ht="36.75" spans="1:24">
+      <c r="Y5" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="33" thickBot="1">
       <c r="A6" s="10" t="s">
         <v>93</v>
       </c>
@@ -17353,8 +16744,11 @@
       <c r="X6" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" ht="36.75" spans="1:24">
+      <c r="Y6" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="33" thickBot="1">
       <c r="A7" s="10" t="s">
         <v>94</v>
       </c>
@@ -17427,8 +16821,11 @@
       <c r="X7" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" ht="36.75" spans="1:24">
+      <c r="Y7" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="33" thickBot="1">
       <c r="A8" s="10" t="s">
         <v>95</v>
       </c>
@@ -17501,8 +16898,11 @@
       <c r="X8" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" ht="36.75" spans="1:24">
+      <c r="Y8" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="33" thickBot="1">
       <c r="A9" s="10" t="s">
         <v>96</v>
       </c>
@@ -17575,8 +16975,11 @@
       <c r="X9" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" ht="53.75" spans="1:24">
+      <c r="Y9" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="49" thickBot="1">
       <c r="A10" s="10" t="s">
         <v>91</v>
       </c>
@@ -17649,8 +17052,11 @@
       <c r="X10" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" ht="55" customHeight="1" spans="1:24">
+      <c r="Y10" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="55" customHeight="1" thickBot="1">
       <c r="A11" s="10" t="s">
         <v>97</v>
       </c>
@@ -17723,8 +17129,11 @@
       <c r="X11" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" ht="61" customHeight="1" spans="1:24">
+      <c r="Y11" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="61" customHeight="1" thickBot="1">
       <c r="A12" s="10" t="s">
         <v>98</v>
       </c>
@@ -17797,8 +17206,11 @@
       <c r="X12" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:24">
+      <c r="Y12" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="36" customHeight="1" thickBot="1">
       <c r="A13" s="10" t="s">
         <v>99</v>
       </c>
@@ -17871,8 +17283,11 @@
       <c r="X13" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" ht="36.75" spans="1:24">
+      <c r="Y13" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="33" thickBot="1">
       <c r="A14" s="10" t="s">
         <v>100</v>
       </c>
@@ -17945,8 +17360,11 @@
       <c r="X14" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" ht="36.75" spans="1:24">
+      <c r="Y14" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="33" thickBot="1">
       <c r="A15" s="10" t="s">
         <v>101</v>
       </c>
@@ -18019,8 +17437,11 @@
       <c r="X15" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" ht="53.75" spans="1:24">
+      <c r="Y15" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="49" thickBot="1">
       <c r="A16" s="10" t="s">
         <v>102</v>
       </c>
@@ -18093,8 +17514,11 @@
       <c r="X16" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" ht="53.75" spans="1:24">
+      <c r="Y16" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="49" thickBot="1">
       <c r="A17" s="10" t="s">
         <v>103</v>
       </c>
@@ -18167,8 +17591,11 @@
       <c r="X17" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" ht="53.75" spans="1:24">
+      <c r="Y17" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="49" thickBot="1">
       <c r="A18" s="10" t="s">
         <v>104</v>
       </c>
@@ -18241,8 +17668,11 @@
       <c r="X18" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" ht="53.75" spans="1:24">
+      <c r="Y18" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="49" thickBot="1">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -18315,8 +17745,11 @@
       <c r="X19" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" ht="53.75" spans="1:24">
+      <c r="Y19" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="49" thickBot="1">
       <c r="A20" s="10" t="s">
         <v>106</v>
       </c>
@@ -18389,8 +17822,11 @@
       <c r="X20" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" ht="53.75" spans="1:24">
+      <c r="Y20" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="49" thickBot="1">
       <c r="A21" s="10" t="s">
         <v>107</v>
       </c>
@@ -18463,8 +17899,11 @@
       <c r="X21" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" ht="53.75" spans="1:24">
+      <c r="Y21" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="49" thickBot="1">
       <c r="A22" s="10" t="s">
         <v>108</v>
       </c>
@@ -18537,8 +17976,11 @@
       <c r="X22" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" ht="36.75" spans="1:24">
+      <c r="Y22" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="33" thickBot="1">
       <c r="A23" s="9" t="s">
         <v>109</v>
       </c>
@@ -18611,8 +18053,11 @@
       <c r="X23" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" ht="53.75" spans="1:24">
+      <c r="Y23" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="49" thickBot="1">
       <c r="A24" s="9" t="s">
         <v>110</v>
       </c>
@@ -18685,23 +18130,101 @@
       <c r="X24" s="12" t="s">
         <v>47</v>
       </c>
+      <c r="Y24" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="33" thickBot="1">
+      <c r="A25" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="T25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="U25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="V25" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="W25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="X25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y25" s="12" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.16071428571429" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="9.16071428571429" customWidth="1"/>
+    <col min="1" max="6" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.75" customHeight="1" spans="1:6">
+    <row r="1" spans="1:6" ht="36.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -18721,7 +18244,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" ht="36.75" customHeight="1" spans="1:6">
+    <row r="2" spans="1:6" ht="36.75" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>111</v>
       </c>
@@ -18741,7 +18264,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="36.75" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" ht="36.75" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>112</v>
       </c>
@@ -18761,7 +18284,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="36.75" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" ht="36.75" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>113</v>
       </c>
@@ -18781,7 +18304,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="36.75" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" ht="36.75" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>114</v>
       </c>
@@ -18801,7 +18324,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="36.75" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" ht="36.75" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>115</v>
       </c>
@@ -18823,17 +18346,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.16071428571429" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="36.75" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -18853,7 +18374,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="2" ht="36.75" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>116</v>
       </c>
@@ -18873,7 +18394,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="36.75" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>117</v>
       </c>
@@ -18893,7 +18414,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="36.75" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>118</v>
       </c>
@@ -18913,7 +18434,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="36.75" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>119</v>
       </c>
@@ -18933,7 +18454,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="36.75" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>120</v>
       </c>
@@ -18955,17 +18476,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.16071428571429" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="36.75" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -18985,7 +18504,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" ht="36.75" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>121</v>
       </c>
@@ -19005,7 +18524,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="36.75" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>122</v>
       </c>
@@ -19025,7 +18544,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="36.75" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>123</v>
       </c>
@@ -19045,7 +18564,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="36.75" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>124</v>
       </c>
@@ -19065,7 +18584,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="36.75" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>125</v>
       </c>
@@ -19087,17 +18606,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="36.75" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -19117,7 +18634,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" ht="36.75" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>126</v>
       </c>
@@ -19137,7 +18654,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="36.75" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>127</v>
       </c>
@@ -19157,7 +18674,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="36.75" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>128</v>
       </c>
@@ -19177,7 +18694,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="36.75" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>129</v>
       </c>
@@ -19197,7 +18714,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="36.75" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>130</v>
       </c>
@@ -19219,17 +18736,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="36.75" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -19249,7 +18764,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" ht="36.75" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>131</v>
       </c>
@@ -19269,7 +18784,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="36.75" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>132</v>
       </c>
@@ -19289,7 +18804,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="36.75" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>133</v>
       </c>
@@ -19309,7 +18824,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="36.75" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>134</v>
       </c>
@@ -19329,7 +18844,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="36.75" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>135</v>
       </c>
@@ -19351,20 +18866,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="71.75" spans="1:20">
+    <row r="1" spans="1:20" ht="80">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19426,7 +18939,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="2" ht="36.75" spans="1:20">
+    <row r="2" spans="1:20" ht="32">
       <c r="A2" s="1" t="s">
         <v>136</v>
       </c>
@@ -19488,7 +19001,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="36.75" spans="1:20">
+    <row r="3" spans="1:20" ht="32">
       <c r="A3" s="1" t="s">
         <v>137</v>
       </c>
@@ -19550,7 +19063,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="36.75" spans="1:20">
+    <row r="4" spans="1:20" ht="32">
       <c r="A4" s="1" t="s">
         <v>138</v>
       </c>
@@ -19612,7 +19125,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="36.75" spans="1:20">
+    <row r="5" spans="1:20" ht="32">
       <c r="A5" s="1" t="s">
         <v>139</v>
       </c>
@@ -19674,7 +19187,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="36.75" spans="1:20">
+    <row r="6" spans="1:20" ht="32">
       <c r="A6" s="1" t="s">
         <v>140</v>
       </c>
@@ -19736,7 +19249,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="36.75" spans="1:20">
+    <row r="7" spans="1:20" ht="32">
       <c r="A7" s="1" t="s">
         <v>141</v>
       </c>
@@ -19798,7 +19311,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" ht="36.75" spans="1:20">
+    <row r="8" spans="1:20" ht="32">
       <c r="A8" s="1" t="s">
         <v>142</v>
       </c>
@@ -19860,7 +19373,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="36.75" spans="1:20">
+    <row r="9" spans="1:20" ht="32">
       <c r="A9" s="1" t="s">
         <v>143</v>
       </c>
@@ -19922,7 +19435,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" ht="36.75" spans="1:20">
+    <row r="10" spans="1:20" ht="32">
       <c r="A10" s="1" t="s">
         <v>144</v>
       </c>
@@ -19984,7 +19497,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="36.75" spans="1:20">
+    <row r="11" spans="1:20" ht="32">
       <c r="A11" s="1" t="s">
         <v>145</v>
       </c>
@@ -20046,7 +19559,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="36.75" spans="1:20">
+    <row r="12" spans="1:20" ht="32">
       <c r="A12" s="1" t="s">
         <v>146</v>
       </c>
@@ -20108,7 +19621,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" ht="36.75" spans="1:20">
+    <row r="13" spans="1:20" ht="32">
       <c r="A13" s="1" t="s">
         <v>147</v>
       </c>
@@ -20170,7 +19683,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="36.75" spans="1:20">
+    <row r="14" spans="1:20" ht="32">
       <c r="A14" s="1" t="s">
         <v>148</v>
       </c>
@@ -20232,7 +19745,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" ht="53.75" spans="1:20">
+    <row r="15" spans="1:20" ht="48">
       <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
@@ -20294,7 +19807,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="36.75" spans="1:20">
+    <row r="16" spans="1:20" ht="32">
       <c r="A16" s="1" t="s">
         <v>150</v>
       </c>
@@ -20356,7 +19869,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" ht="36.75" spans="1:20">
+    <row r="17" spans="1:20" ht="32">
       <c r="A17" s="1" t="s">
         <v>151</v>
       </c>
@@ -20418,7 +19931,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" ht="36.75" spans="1:20">
+    <row r="18" spans="1:20" ht="32">
       <c r="A18" s="1" t="s">
         <v>152</v>
       </c>
@@ -20480,7 +19993,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" ht="36.75" spans="1:20">
+    <row r="19" spans="1:20" ht="32">
       <c r="A19" s="1" t="s">
         <v>153</v>
       </c>
@@ -20542,7 +20055,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" ht="36.75" spans="1:20">
+    <row r="20" spans="1:20" ht="32">
       <c r="A20" s="1" t="s">
         <v>154</v>
       </c>
@@ -20606,6 +20119,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/dbm-ui/backend/ticket/exclusive_ticket.xlsx
+++ b/dbm-ui/backend/ticket/exclusive_ticket.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10905"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevnzheng/Projects/blueking-dbm/dbm-ui/backend/ticket/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4421548-4D1C-D241-9785-881F680D53C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="760" windowWidth="30220" windowHeight="20140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="30720" windowHeight="12780"/>
   </bookViews>
   <sheets>
     <sheet name="cluster_mysql_exclusive" sheetId="1" r:id="rId1"/>
@@ -100,7 +94,7 @@
     <t>MySQL 添加Proxy</t>
   </si>
   <si>
-    <t>MySQL 缩容Proxy</t>
+    <t>MySQL 减少Proxy</t>
   </si>
   <si>
     <t>MySQL 接入 CLB</t>
@@ -376,6 +370,9 @@
     <t>Redis 故障自愈-实例下架</t>
   </si>
   <si>
+    <t>Redis 容灾演练</t>
+  </si>
+  <si>
     <t>Kafka 集群扩容</t>
   </si>
   <si>
@@ -507,19 +504,22 @@
   <si>
     <t>SQLServer 集群授权</t>
   </si>
-  <si>
-    <t>Redis 容灾演练</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -539,7 +539,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -585,12 +585,163 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -609,8 +760,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -746,9 +1083,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -837,11 +1416,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -863,17 +1442,61 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1131,40 +1754,40 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AU201"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.66666666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="1" max="1" width="21.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.1666666666667" customWidth="1"/>
     <col min="3" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.3333333333333" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" customWidth="1"/>
+    <col min="7" max="7" width="7.66666666666667" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="13.33203125" customWidth="1"/>
+    <col min="9" max="9" width="13.3333333333333" customWidth="1"/>
     <col min="10" max="11" width="9.5" customWidth="1"/>
-    <col min="12" max="13" width="7.6640625" customWidth="1"/>
-    <col min="14" max="15" width="10.33203125" customWidth="1"/>
-    <col min="16" max="16" width="10.1640625" customWidth="1"/>
-    <col min="17" max="18" width="10.33203125" customWidth="1"/>
-    <col min="19" max="19" width="7.6640625" customWidth="1"/>
-    <col min="20" max="21" width="9.6640625" customWidth="1"/>
+    <col min="12" max="13" width="7.66666666666667" customWidth="1"/>
+    <col min="14" max="15" width="10.3333333333333" customWidth="1"/>
+    <col min="16" max="16" width="10.1666666666667" customWidth="1"/>
+    <col min="17" max="18" width="10.3333333333333" customWidth="1"/>
+    <col min="19" max="19" width="7.66666666666667" customWidth="1"/>
+    <col min="20" max="21" width="9.66666666666667" customWidth="1"/>
     <col min="22" max="30" width="9.5" customWidth="1"/>
-    <col min="31" max="31" width="7.6640625" customWidth="1"/>
+    <col min="31" max="31" width="7.66666666666667" customWidth="1"/>
     <col min="32" max="32" width="9.5" customWidth="1"/>
     <col min="33" max="33" width="12.5" customWidth="1"/>
-    <col min="34" max="34" width="13.6640625" customWidth="1"/>
+    <col min="34" max="34" width="13.6666666666667" customWidth="1"/>
     <col min="35" max="38" width="12.5" customWidth="1"/>
-    <col min="39" max="40" width="14.6640625" customWidth="1"/>
+    <col min="39" max="40" width="14.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="64">
+    <row r="1" ht="78" spans="1:47">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1307,7 +1930,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="16">
+    <row r="2" ht="15.6" spans="1:47">
       <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
@@ -1450,7 +2073,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="32">
+    <row r="3" ht="31.2" spans="1:47">
       <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +2216,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="32">
+    <row r="4" ht="31.2" spans="1:47">
       <c r="A4" s="31" t="s">
         <v>3</v>
       </c>
@@ -1736,7 +2359,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="16">
+    <row r="5" ht="15.6" spans="1:47">
       <c r="A5" s="31" t="s">
         <v>6</v>
       </c>
@@ -1879,7 +2502,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="32">
+    <row r="6" ht="31.2" spans="1:47">
       <c r="A6" s="31" t="s">
         <v>5</v>
       </c>
@@ -2022,7 +2645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="16">
+    <row r="7" ht="15.6" spans="1:47">
       <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
@@ -2165,7 +2788,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="16">
+    <row r="8" ht="15.6" spans="1:47">
       <c r="A8" s="31" t="s">
         <v>7</v>
       </c>
@@ -2308,7 +2931,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="16">
+    <row r="9" ht="15.6" spans="1:47">
       <c r="A9" s="31" t="s">
         <v>8</v>
       </c>
@@ -2451,7 +3074,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="16">
+    <row r="10" ht="15.6" spans="1:47">
       <c r="A10" s="31" t="s">
         <v>9</v>
       </c>
@@ -2594,7 +3217,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="16">
+    <row r="11" ht="15.6" spans="1:47">
       <c r="A11" s="31" t="s">
         <v>10</v>
       </c>
@@ -2737,7 +3360,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="16">
+    <row r="12" ht="15.6" spans="1:47">
       <c r="A12" s="31" t="s">
         <v>11</v>
       </c>
@@ -2880,7 +3503,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="16">
+    <row r="13" ht="15.6" spans="1:47">
       <c r="A13" s="31" t="s">
         <v>12</v>
       </c>
@@ -3023,7 +3646,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="16">
+    <row r="14" ht="15.6" spans="1:47">
       <c r="A14" s="31" t="s">
         <v>13</v>
       </c>
@@ -3166,7 +3789,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="16">
+    <row r="15" ht="15.6" spans="1:47">
       <c r="A15" s="31" t="s">
         <v>14</v>
       </c>
@@ -3309,7 +3932,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="32">
+    <row r="16" ht="31.2" spans="1:47">
       <c r="A16" s="31" t="s">
         <v>15</v>
       </c>
@@ -3452,7 +4075,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="16">
+    <row r="17" ht="15.6" spans="1:47">
       <c r="A17" s="31" t="s">
         <v>16</v>
       </c>
@@ -3595,7 +4218,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:47" ht="16">
+    <row r="18" ht="15.6" spans="1:47">
       <c r="A18" s="31" t="s">
         <v>17</v>
       </c>
@@ -3738,7 +4361,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:47" ht="16">
+    <row r="19" ht="15.6" spans="1:47">
       <c r="A19" s="31" t="s">
         <v>18</v>
       </c>
@@ -3881,7 +4504,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:47" ht="16">
+    <row r="20" ht="15.6" spans="1:47">
       <c r="A20" s="31" t="s">
         <v>19</v>
       </c>
@@ -4024,7 +4647,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:47" ht="16">
+    <row r="21" ht="15.6" spans="1:47">
       <c r="A21" s="31" t="s">
         <v>20</v>
       </c>
@@ -4167,7 +4790,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:47" ht="16">
+    <row r="22" ht="15.6" spans="1:47">
       <c r="A22" s="31" t="s">
         <v>21</v>
       </c>
@@ -4310,7 +4933,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:47" ht="16">
+    <row r="23" ht="15.6" spans="1:47">
       <c r="A23" s="31" t="s">
         <v>22</v>
       </c>
@@ -4453,7 +5076,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:47" ht="16">
+    <row r="24" ht="31.2" spans="1:47">
       <c r="A24" s="31" t="s">
         <v>23</v>
       </c>
@@ -4596,7 +5219,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:47" ht="16">
+    <row r="25" ht="15.6" spans="1:47">
       <c r="A25" s="31" t="s">
         <v>24</v>
       </c>
@@ -4739,7 +5362,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:47" ht="16">
+    <row r="26" ht="15.6" spans="1:47">
       <c r="A26" s="31" t="s">
         <v>25</v>
       </c>
@@ -4882,7 +5505,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:47" ht="32">
+    <row r="27" ht="31.2" spans="1:47">
       <c r="A27" s="31" t="s">
         <v>26</v>
       </c>
@@ -5025,7 +5648,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="32">
+    <row r="28" ht="31.2" spans="1:47">
       <c r="A28" s="31" t="s">
         <v>27</v>
       </c>
@@ -5168,7 +5791,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:47" ht="32">
+    <row r="29" ht="31.2" spans="1:47">
       <c r="A29" s="31" t="s">
         <v>28</v>
       </c>
@@ -5311,7 +5934,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:47" ht="32">
+    <row r="30" ht="31.2" spans="1:47">
       <c r="A30" s="31" t="s">
         <v>29</v>
       </c>
@@ -5454,7 +6077,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:47" ht="16">
+    <row r="31" ht="15.6" spans="1:47">
       <c r="A31" s="31" t="s">
         <v>30</v>
       </c>
@@ -5597,7 +6220,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:47" ht="16">
+    <row r="32" ht="31.2" spans="1:47">
       <c r="A32" s="31" t="s">
         <v>31</v>
       </c>
@@ -5740,7 +6363,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:47" ht="16">
+    <row r="33" ht="31.2" spans="1:47">
       <c r="A33" s="31" t="s">
         <v>32</v>
       </c>
@@ -5883,7 +6506,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:47" ht="16">
+    <row r="34" ht="15.6" spans="1:47">
       <c r="A34" s="31" t="s">
         <v>33</v>
       </c>
@@ -6026,7 +6649,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:47" ht="16">
+    <row r="35" ht="15.6" spans="1:47">
       <c r="A35" s="31" t="s">
         <v>34</v>
       </c>
@@ -6169,7 +6792,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:47" ht="16">
+    <row r="36" ht="31.2" spans="1:47">
       <c r="A36" s="31" t="s">
         <v>35</v>
       </c>
@@ -6312,7 +6935,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:47" ht="16">
+    <row r="37" ht="15.6" spans="1:47">
       <c r="A37" s="31" t="s">
         <v>36</v>
       </c>
@@ -6455,7 +7078,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:47" ht="16">
+    <row r="38" ht="31.2" spans="1:47">
       <c r="A38" s="31" t="s">
         <v>37</v>
       </c>
@@ -6598,7 +7221,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:47" ht="16">
+    <row r="39" ht="15.6" spans="1:47">
       <c r="A39" s="31" t="s">
         <v>38</v>
       </c>
@@ -6741,7 +7364,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:47" ht="16">
+    <row r="40" ht="15.6" spans="1:47">
       <c r="A40" s="31" t="s">
         <v>39</v>
       </c>
@@ -6884,7 +7507,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:47" ht="16">
+    <row r="41" ht="15.6" spans="1:47">
       <c r="A41" s="31" t="s">
         <v>40</v>
       </c>
@@ -7027,7 +7650,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:47" ht="16">
+    <row r="42" ht="15.6" spans="1:47">
       <c r="A42" s="31" t="s">
         <v>41</v>
       </c>
@@ -7170,7 +7793,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:47" ht="16">
+    <row r="43" ht="15.6" spans="1:47">
       <c r="A43" s="31" t="s">
         <v>42</v>
       </c>
@@ -7313,7 +7936,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:47" ht="16">
+    <row r="44" ht="15.6" spans="1:47">
       <c r="A44" s="31" t="s">
         <v>43</v>
       </c>
@@ -7456,7 +8079,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:47" ht="16">
+    <row r="45" ht="15.6" spans="1:47">
       <c r="A45" s="31" t="s">
         <v>44</v>
       </c>
@@ -7599,7 +8222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:47" ht="32">
+    <row r="46" ht="31.2" spans="1:47">
       <c r="A46" s="31" t="s">
         <v>45</v>
       </c>
@@ -7742,7 +8365,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="1:47" ht="32">
+    <row r="47" ht="31.2" spans="1:47">
       <c r="A47" s="31" t="s">
         <v>46</v>
       </c>
@@ -7885,7 +8508,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:47">
+    <row r="48" spans="1:19">
       <c r="A48" s="35"/>
       <c r="B48" s="35"/>
       <c r="C48" s="35"/>
@@ -11121,31 +11744,33 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AO41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.6666666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="5" width="14.1640625" customWidth="1"/>
+    <col min="1" max="1" width="19.8333333333333" customWidth="1"/>
+    <col min="2" max="5" width="14.1666666666667" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="11" width="14.1640625" customWidth="1"/>
+    <col min="7" max="11" width="14.1666666666667" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="18" width="14.1640625" customWidth="1"/>
+    <col min="14" max="18" width="14.1666666666667" customWidth="1"/>
     <col min="19" max="19" width="19" customWidth="1"/>
-    <col min="20" max="21" width="9.6640625" customWidth="1"/>
-    <col min="22" max="24" width="9.83203125" customWidth="1"/>
-    <col min="25" max="25" width="10.6640625" customWidth="1"/>
-    <col min="26" max="31" width="9.83203125" customWidth="1"/>
-    <col min="32" max="32" width="10.1640625" customWidth="1"/>
-    <col min="33" max="35" width="9.83203125" customWidth="1"/>
+    <col min="20" max="21" width="9.66666666666667" customWidth="1"/>
+    <col min="22" max="24" width="9.83333333333333" customWidth="1"/>
+    <col min="25" max="25" width="10.6666666666667" customWidth="1"/>
+    <col min="26" max="31" width="9.83333333333333" customWidth="1"/>
+    <col min="32" max="32" width="10.1666666666667" customWidth="1"/>
+    <col min="33" max="35" width="9.83333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="64">
+    <row r="1" ht="78" spans="1:41">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -11270,7 +11895,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:41" ht="32">
+    <row r="2" ht="31.2" spans="1:41">
       <c r="A2" s="21" t="s">
         <v>49</v>
       </c>
@@ -11395,7 +12020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:41" ht="32">
+    <row r="3" ht="31.2" spans="1:41">
       <c r="A3" s="21" t="s">
         <v>50</v>
       </c>
@@ -11520,7 +12145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:41" ht="32">
+    <row r="4" ht="31.2" spans="1:41">
       <c r="A4" s="21" t="s">
         <v>51</v>
       </c>
@@ -11645,7 +12270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:41" ht="16">
+    <row r="5" ht="31.2" spans="1:41">
       <c r="A5" s="21" t="s">
         <v>52</v>
       </c>
@@ -11770,7 +12395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:41" ht="16">
+    <row r="6" ht="31.2" spans="1:41">
       <c r="A6" s="21" t="s">
         <v>53</v>
       </c>
@@ -11895,7 +12520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:41" ht="32">
+    <row r="7" ht="31.2" spans="1:41">
       <c r="A7" s="21" t="s">
         <v>54</v>
       </c>
@@ -12020,7 +12645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:41" ht="32">
+    <row r="8" ht="31.2" spans="1:41">
       <c r="A8" s="21" t="s">
         <v>55</v>
       </c>
@@ -12145,7 +12770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:41" ht="32">
+    <row r="9" ht="31.2" spans="1:41">
       <c r="A9" s="21" t="s">
         <v>56</v>
       </c>
@@ -12270,7 +12895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:41" ht="16">
+    <row r="10" ht="31.2" spans="1:41">
       <c r="A10" s="21" t="s">
         <v>57</v>
       </c>
@@ -12395,7 +13020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:41" ht="32">
+    <row r="11" ht="31.2" spans="1:41">
       <c r="A11" s="21" t="s">
         <v>58</v>
       </c>
@@ -12520,7 +13145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:41" ht="32">
+    <row r="12" ht="31.2" spans="1:41">
       <c r="A12" s="21" t="s">
         <v>59</v>
       </c>
@@ -12645,7 +13270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:41" ht="32">
+    <row r="13" ht="31.2" spans="1:41">
       <c r="A13" s="21" t="s">
         <v>60</v>
       </c>
@@ -12685,10 +13310,10 @@
       <c r="M13" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="N13" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="O13" s="29" t="s">
+      <c r="N13" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O13" s="28" t="s">
         <v>48</v>
       </c>
       <c r="P13" s="24" t="s">
@@ -12703,7 +13328,7 @@
       <c r="S13" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="T13" s="29" t="s">
+      <c r="T13" s="28" t="s">
         <v>48</v>
       </c>
       <c r="U13" s="24" t="s">
@@ -12770,7 +13395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:41" ht="32">
+    <row r="14" ht="31.2" spans="1:41">
       <c r="A14" s="21" t="s">
         <v>61</v>
       </c>
@@ -12807,13 +13432,13 @@
       <c r="L14" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="M14" s="29" t="s">
+      <c r="M14" s="28" t="s">
         <v>48</v>
       </c>
       <c r="N14" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="O14" s="29" t="s">
+      <c r="O14" s="28" t="s">
         <v>48</v>
       </c>
       <c r="P14" s="24" t="s">
@@ -12828,7 +13453,7 @@
       <c r="S14" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="T14" s="29" t="s">
+      <c r="T14" s="28" t="s">
         <v>48</v>
       </c>
       <c r="U14" s="24" t="s">
@@ -12895,7 +13520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:41" ht="32">
+    <row r="15" ht="31.2" spans="1:41">
       <c r="A15" s="21" t="s">
         <v>62</v>
       </c>
@@ -12932,10 +13557,10 @@
       <c r="L15" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="M15" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15" s="29" t="s">
+      <c r="M15" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="28" t="s">
         <v>48</v>
       </c>
       <c r="O15" s="25" t="s">
@@ -12953,7 +13578,7 @@
       <c r="S15" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="T15" s="29" t="s">
+      <c r="T15" s="28" t="s">
         <v>48</v>
       </c>
       <c r="U15" s="24" t="s">
@@ -13020,7 +13645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:41" ht="32">
+    <row r="16" ht="31.2" spans="1:41">
       <c r="A16" s="21" t="s">
         <v>63</v>
       </c>
@@ -13145,7 +13770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:41" ht="32">
+    <row r="17" ht="31.2" spans="1:41">
       <c r="A17" s="21" t="s">
         <v>64</v>
       </c>
@@ -13270,7 +13895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:41" ht="32">
+    <row r="18" ht="31.2" spans="1:41">
       <c r="A18" s="21" t="s">
         <v>65</v>
       </c>
@@ -13395,7 +14020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:41" ht="32">
+    <row r="19" ht="31.2" spans="1:41">
       <c r="A19" s="21" t="s">
         <v>66</v>
       </c>
@@ -13520,7 +14145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:41" ht="32">
+    <row r="20" ht="31.2" spans="1:41">
       <c r="A20" s="21" t="s">
         <v>67</v>
       </c>
@@ -13560,10 +14185,10 @@
       <c r="M20" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="N20" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="O20" s="29" t="s">
+      <c r="N20" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O20" s="28" t="s">
         <v>48</v>
       </c>
       <c r="P20" s="24" t="s">
@@ -13645,7 +14270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:41" ht="32">
+    <row r="21" ht="31.2" spans="1:41">
       <c r="A21" s="21" t="s">
         <v>68</v>
       </c>
@@ -13770,7 +14395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:41" ht="32">
+    <row r="22" ht="31.2" spans="1:41">
       <c r="A22" s="21" t="s">
         <v>69</v>
       </c>
@@ -13895,7 +14520,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:41" ht="32">
+    <row r="23" ht="31.2" spans="1:41">
       <c r="A23" s="21" t="s">
         <v>70</v>
       </c>
@@ -14020,7 +14645,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:41" ht="32">
+    <row r="24" ht="31.2" spans="1:41">
       <c r="A24" s="21" t="s">
         <v>71</v>
       </c>
@@ -14145,7 +14770,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:41" ht="32">
+    <row r="25" ht="31.2" spans="1:41">
       <c r="A25" s="21" t="s">
         <v>72</v>
       </c>
@@ -14270,7 +14895,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:41" ht="32">
+    <row r="26" ht="31.2" spans="1:41">
       <c r="A26" s="21" t="s">
         <v>73</v>
       </c>
@@ -14395,7 +15020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:41" ht="32">
+    <row r="27" ht="31.2" spans="1:41">
       <c r="A27" s="21" t="s">
         <v>74</v>
       </c>
@@ -14520,7 +15145,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:41" ht="32">
+    <row r="28" ht="31.2" spans="1:41">
       <c r="A28" s="21" t="s">
         <v>75</v>
       </c>
@@ -14645,7 +15270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:41" ht="32">
+    <row r="29" ht="31.2" spans="1:41">
       <c r="A29" s="21" t="s">
         <v>76</v>
       </c>
@@ -14770,7 +15395,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:41" ht="32">
+    <row r="30" ht="31.2" spans="1:41">
       <c r="A30" s="21" t="s">
         <v>77</v>
       </c>
@@ -14864,7 +15489,7 @@
       <c r="AE30" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="AF30" s="29" t="s">
+      <c r="AF30" s="28" t="s">
         <v>47</v>
       </c>
       <c r="AG30" s="24" t="s">
@@ -14891,11 +15516,11 @@
       <c r="AN30" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="AO30" s="29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:41" ht="16">
+      <c r="AO30" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" ht="31.2" spans="1:41">
       <c r="A31" s="21" t="s">
         <v>78</v>
       </c>
@@ -14989,7 +15614,7 @@
       <c r="AE31" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="AF31" s="29" t="s">
+      <c r="AF31" s="28" t="s">
         <v>47</v>
       </c>
       <c r="AG31" s="21" t="s">
@@ -15016,11 +15641,11 @@
       <c r="AN31" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="AO31" s="29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:41" ht="32">
+      <c r="AO31" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" ht="31.2" spans="1:41">
       <c r="A32" s="21" t="s">
         <v>79</v>
       </c>
@@ -15045,7 +15670,7 @@
       <c r="H32" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="I32" s="28"/>
+      <c r="I32" s="29"/>
       <c r="J32" s="24" t="s">
         <v>47</v>
       </c>
@@ -15109,7 +15734,7 @@
       <c r="AD32" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="AE32" s="29" t="s">
+      <c r="AE32" s="28" t="s">
         <v>47</v>
       </c>
       <c r="AF32" s="25" t="s">
@@ -15139,11 +15764,11 @@
       <c r="AN32" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="AO32" s="29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:41" ht="32">
+      <c r="AO32" s="28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" ht="31.2" spans="1:41">
       <c r="A33" s="21" t="s">
         <v>80</v>
       </c>
@@ -15268,7 +15893,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:41" ht="32">
+    <row r="34" ht="31.2" spans="1:41">
       <c r="A34" s="21" t="s">
         <v>81</v>
       </c>
@@ -15393,7 +16018,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:41" ht="32">
+    <row r="35" ht="31.2" spans="1:41">
       <c r="A35" s="21" t="s">
         <v>82</v>
       </c>
@@ -15518,7 +16143,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:41" ht="32">
+    <row r="36" ht="31.2" spans="1:41">
       <c r="A36" s="21" t="s">
         <v>83</v>
       </c>
@@ -15643,7 +16268,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:41" ht="32">
+    <row r="37" ht="31.2" spans="1:41">
       <c r="A37" s="21" t="s">
         <v>84</v>
       </c>
@@ -15768,7 +16393,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:41" ht="32">
+    <row r="38" ht="31.2" spans="1:41">
       <c r="A38" s="21" t="s">
         <v>85</v>
       </c>
@@ -15893,7 +16518,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:41" ht="32">
+    <row r="39" ht="31.2" spans="1:41">
       <c r="A39" s="21" t="s">
         <v>86</v>
       </c>
@@ -16018,7 +16643,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:41" ht="32">
+    <row r="40" ht="31.2" spans="1:41">
       <c r="A40" s="21" t="s">
         <v>87</v>
       </c>
@@ -16143,7 +16768,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:41" ht="32">
+    <row r="41" ht="31.2" spans="1:41">
       <c r="A41" s="21" t="s">
         <v>88</v>
       </c>
@@ -16234,10 +16859,10 @@
       <c r="AD41" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="AE41" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF41" s="29" t="s">
+      <c r="AE41" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF41" s="28" t="s">
         <v>47</v>
       </c>
       <c r="AG41" s="21" t="s">
@@ -16270,23 +16895,25 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Y25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="8.66666666666667" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="9.33203125" customWidth="1"/>
-    <col min="14" max="15" width="10.6640625" customWidth="1"/>
-    <col min="16" max="21" width="9.6640625" customWidth="1"/>
+    <col min="13" max="13" width="9.33333333333333" customWidth="1"/>
+    <col min="14" max="15" width="10.6666666666667" customWidth="1"/>
+    <col min="16" max="21" width="9.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="49" thickBot="1">
+    <row r="1" ht="63.15" spans="1:25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16360,10 +16987,10 @@
         <v>110</v>
       </c>
       <c r="Y1" s="16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="33" thickBot="1">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" ht="47.55" spans="1:25">
       <c r="A2" s="10" t="s">
         <v>89</v>
       </c>
@@ -16440,7 +17067,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="33" thickBot="1">
+    <row r="3" ht="47.55" spans="1:25">
       <c r="A3" s="10" t="s">
         <v>90</v>
       </c>
@@ -16517,7 +17144,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="49" thickBot="1">
+    <row r="4" ht="47.55" spans="1:25">
       <c r="A4" s="10" t="s">
         <v>91</v>
       </c>
@@ -16594,7 +17221,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="33" thickBot="1">
+    <row r="5" ht="47.55" spans="1:25">
       <c r="A5" s="10" t="s">
         <v>92</v>
       </c>
@@ -16671,7 +17298,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="33" thickBot="1">
+    <row r="6" ht="47.55" spans="1:25">
       <c r="A6" s="10" t="s">
         <v>93</v>
       </c>
@@ -16748,7 +17375,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="33" thickBot="1">
+    <row r="7" ht="47.55" spans="1:25">
       <c r="A7" s="10" t="s">
         <v>94</v>
       </c>
@@ -16825,7 +17452,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="33" thickBot="1">
+    <row r="8" ht="47.55" spans="1:25">
       <c r="A8" s="10" t="s">
         <v>95</v>
       </c>
@@ -16902,7 +17529,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="33" thickBot="1">
+    <row r="9" ht="47.55" spans="1:25">
       <c r="A9" s="10" t="s">
         <v>96</v>
       </c>
@@ -16979,7 +17606,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="49" thickBot="1">
+    <row r="10" ht="47.55" spans="1:25">
       <c r="A10" s="10" t="s">
         <v>91</v>
       </c>
@@ -17056,7 +17683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="55" customHeight="1" thickBot="1">
+    <row r="11" ht="55" customHeight="1" spans="1:25">
       <c r="A11" s="10" t="s">
         <v>97</v>
       </c>
@@ -17133,7 +17760,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="61" customHeight="1" thickBot="1">
+    <row r="12" ht="61" customHeight="1" spans="1:25">
       <c r="A12" s="10" t="s">
         <v>98</v>
       </c>
@@ -17210,7 +17837,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="36" customHeight="1" thickBot="1">
+    <row r="13" ht="36" customHeight="1" spans="1:25">
       <c r="A13" s="10" t="s">
         <v>99</v>
       </c>
@@ -17287,7 +17914,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="33" thickBot="1">
+    <row r="14" ht="47.55" spans="1:25">
       <c r="A14" s="10" t="s">
         <v>100</v>
       </c>
@@ -17364,7 +17991,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="33" thickBot="1">
+    <row r="15" ht="47.55" spans="1:25">
       <c r="A15" s="10" t="s">
         <v>101</v>
       </c>
@@ -17441,7 +18068,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="49" thickBot="1">
+    <row r="16" ht="63.15" spans="1:25">
       <c r="A16" s="10" t="s">
         <v>102</v>
       </c>
@@ -17518,7 +18145,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="49" thickBot="1">
+    <row r="17" ht="47.55" spans="1:25">
       <c r="A17" s="10" t="s">
         <v>103</v>
       </c>
@@ -17595,7 +18222,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="49" thickBot="1">
+    <row r="18" ht="47.55" spans="1:25">
       <c r="A18" s="10" t="s">
         <v>104</v>
       </c>
@@ -17672,7 +18299,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="49" thickBot="1">
+    <row r="19" ht="47.55" spans="1:25">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -17749,7 +18376,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="49" thickBot="1">
+    <row r="20" ht="63.15" spans="1:25">
       <c r="A20" s="10" t="s">
         <v>106</v>
       </c>
@@ -17826,7 +18453,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="49" thickBot="1">
+    <row r="21" ht="63.15" spans="1:25">
       <c r="A21" s="10" t="s">
         <v>107</v>
       </c>
@@ -17903,7 +18530,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="49" thickBot="1">
+    <row r="22" ht="63.15" spans="1:25">
       <c r="A22" s="10" t="s">
         <v>108</v>
       </c>
@@ -17980,7 +18607,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="33" thickBot="1">
+    <row r="23" ht="47.55" spans="1:25">
       <c r="A23" s="9" t="s">
         <v>109</v>
       </c>
@@ -18057,7 +18684,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="49" thickBot="1">
+    <row r="24" ht="63.15" spans="1:25">
       <c r="A24" s="9" t="s">
         <v>110</v>
       </c>
@@ -18134,9 +18761,9 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="33" thickBot="1">
+    <row r="25" ht="47.55" spans="1:25">
       <c r="A25" s="9" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>48</v>
@@ -18213,101 +18840,103 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="6" width="9.1640625" customWidth="1"/>
+    <col min="1" max="6" width="9.16666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36.75" customHeight="1">
+    <row r="1" ht="36.75" customHeight="1" spans="1:6">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" ht="36.75" customHeight="1" spans="1:6">
+      <c r="A2" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="36.75" customHeight="1" spans="1:6">
+      <c r="A3" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" ht="36.75" customHeight="1" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="B4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="36.75" customHeight="1" spans="1:6">
+      <c r="A5" s="6" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="36.75" customHeight="1">
-      <c r="A5" s="6" t="s">
-        <v>114</v>
-      </c>
       <c r="B5" s="8" t="s">
         <v>48</v>
       </c>
@@ -18324,9 +18953,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="36.75" customHeight="1">
+    <row r="6" ht="36.75" customHeight="1" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>48</v>
@@ -18346,98 +18975,100 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="32">
+    <row r="1" ht="47.55" spans="1:6">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" ht="47.55" spans="1:6">
+      <c r="A2" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="47.55" spans="1:6">
+      <c r="A3" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" ht="47.55" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="B4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="47.55" spans="1:6">
+      <c r="A5" s="6" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="32">
-      <c r="A2" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32">
-      <c r="A3" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="32">
-      <c r="A4" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32">
-      <c r="A5" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="B5" s="8" t="s">
         <v>48</v>
       </c>
@@ -18454,9 +19085,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="32">
+    <row r="6" ht="47.55" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>48</v>
@@ -18476,98 +19107,100 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="32">
+    <row r="1" ht="31.95" spans="1:6">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" ht="31.95" spans="1:6">
+      <c r="A2" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="31.95" spans="1:6">
+      <c r="A3" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" ht="31.95" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="B4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="31.95" spans="1:6">
+      <c r="A5" s="6" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="32">
-      <c r="A2" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32">
-      <c r="A3" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="32">
-      <c r="A4" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32">
-      <c r="A5" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="B5" s="8" t="s">
         <v>48</v>
       </c>
@@ -18584,9 +19217,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="32">
+    <row r="6" ht="31.95" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>48</v>
@@ -18606,98 +19239,100 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="32">
+    <row r="1" ht="31.95" spans="1:6">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" ht="31.95" spans="1:6">
+      <c r="A2" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="31.95" spans="1:6">
+      <c r="A3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" ht="31.95" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="B4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="31.95" spans="1:6">
+      <c r="A5" s="6" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="32">
-      <c r="A2" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32">
-      <c r="A3" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="32">
-      <c r="A4" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32">
-      <c r="A5" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="B5" s="8" t="s">
         <v>48</v>
       </c>
@@ -18714,9 +19349,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="32">
+    <row r="6" ht="31.95" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>48</v>
@@ -18736,98 +19371,100 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="32">
+    <row r="1" ht="31.95" spans="1:6">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" ht="31.95" spans="1:6">
+      <c r="A2" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="B2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" ht="31.95" spans="1:6">
+      <c r="A3" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" ht="31.95" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="B4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" ht="31.95" spans="1:6">
+      <c r="A5" s="6" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="32">
-      <c r="A2" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32">
-      <c r="A3" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="32">
-      <c r="A4" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32">
-      <c r="A5" s="6" t="s">
-        <v>134</v>
-      </c>
       <c r="B5" s="8" t="s">
         <v>48</v>
       </c>
@@ -18844,9 +19481,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="32">
+    <row r="6" ht="31.95" spans="1:6">
       <c r="A6" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>48</v>
@@ -18866,1137 +19503,1139 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:T20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="80">
+    <row r="1" ht="78.75" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="2" ht="31.95" spans="1:20">
+      <c r="A2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" ht="31.95" spans="1:20">
+      <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" ht="31.95" spans="1:20">
+      <c r="A4" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" ht="31.95" spans="1:20">
+      <c r="A5" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" ht="31.95" spans="1:20">
+      <c r="A6" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T6" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" ht="31.95" spans="1:20">
+      <c r="A7" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="B7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" ht="31.95" spans="1:20">
+      <c r="A8" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" ht="31.95" spans="1:20">
+      <c r="A9" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" ht="31.95" spans="1:20">
+      <c r="A10" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" ht="31.95" spans="1:20">
+      <c r="A11" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" ht="31.95" spans="1:20">
+      <c r="A12" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" ht="31.95" spans="1:20">
+      <c r="A13" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="B13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" ht="47.55" spans="1:20">
+      <c r="A14" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="B14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" ht="47.55" spans="1:20">
+      <c r="A15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="B15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" ht="31.95" spans="1:20">
+      <c r="A16" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="B16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" ht="31.95" spans="1:20">
+      <c r="A17" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="B17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" ht="31.95" spans="1:20">
+      <c r="A18" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="B18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" ht="31.95" spans="1:20">
+      <c r="A19" s="1" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="32">
-      <c r="A2" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="32">
-      <c r="A3" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="32">
-      <c r="A4" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="32">
-      <c r="A5" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="32">
-      <c r="A6" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="32">
-      <c r="A7" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="32">
-      <c r="A8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="32">
-      <c r="A9" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="32">
-      <c r="A10" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="32">
-      <c r="A11" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T11" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="32">
-      <c r="A12" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="32">
-      <c r="A13" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T13" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="32">
-      <c r="A14" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="48">
-      <c r="A15" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="R15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="S15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="T15" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="32">
-      <c r="A16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T16" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="32">
-      <c r="A17" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="32">
-      <c r="A18" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="32">
-      <c r="A19" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="B19" s="3" t="s">
         <v>48</v>
       </c>
@@ -20055,9 +20694,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="32">
+    <row r="20" ht="31.95" spans="1:20">
       <c r="A20" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>47</v>
@@ -20119,5 +20758,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/dbm-ui/backend/ticket/exclusive_ticket.xlsx
+++ b/dbm-ui/backend/ticket/exclusive_ticket.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevnzheng/Projects/blueking-dbm/dbm-ui/backend/ticket/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C424F28-81CB-1D43-A86A-861F97018F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="12780"/>
+    <workbookView xWindow="4360" yWindow="680" windowWidth="30200" windowHeight="20060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cluster_mysql_exclusive" sheetId="1" r:id="rId1"/>
@@ -35,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5094" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5145" uniqueCount="157">
   <si>
     <t>能否并行</t>
   </si>
@@ -504,22 +510,19 @@
   <si>
     <t>SQLServer 集群授权</t>
   </si>
+  <si>
+    <t>Redis 回档演练</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="31">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -539,7 +542,7 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -585,163 +588,12 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -760,194 +612,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="19">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1083,251 +749,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1442,61 +866,17 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1754,40 +1134,40 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU201"/>
-  <sheetFormatPr defaultColWidth="9.66666666666667" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21.1666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.1666666666667" customWidth="1"/>
+    <col min="1" max="1" width="21.1640625" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" customWidth="1"/>
     <col min="3" max="4" width="12.5" customWidth="1"/>
-    <col min="5" max="5" width="10.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="7.66666666666667" customWidth="1"/>
+    <col min="7" max="7" width="7.6640625" customWidth="1"/>
     <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="13.3333333333333" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" customWidth="1"/>
     <col min="10" max="11" width="9.5" customWidth="1"/>
-    <col min="12" max="13" width="7.66666666666667" customWidth="1"/>
-    <col min="14" max="15" width="10.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="10.1666666666667" customWidth="1"/>
-    <col min="17" max="18" width="10.3333333333333" customWidth="1"/>
-    <col min="19" max="19" width="7.66666666666667" customWidth="1"/>
-    <col min="20" max="21" width="9.66666666666667" customWidth="1"/>
+    <col min="12" max="13" width="7.6640625" customWidth="1"/>
+    <col min="14" max="15" width="10.33203125" customWidth="1"/>
+    <col min="16" max="16" width="10.1640625" customWidth="1"/>
+    <col min="17" max="18" width="10.33203125" customWidth="1"/>
+    <col min="19" max="19" width="7.6640625" customWidth="1"/>
+    <col min="20" max="21" width="9.6640625" customWidth="1"/>
     <col min="22" max="30" width="9.5" customWidth="1"/>
-    <col min="31" max="31" width="7.66666666666667" customWidth="1"/>
+    <col min="31" max="31" width="7.6640625" customWidth="1"/>
     <col min="32" max="32" width="9.5" customWidth="1"/>
     <col min="33" max="33" width="12.5" customWidth="1"/>
-    <col min="34" max="34" width="13.6666666666667" customWidth="1"/>
+    <col min="34" max="34" width="13.6640625" customWidth="1"/>
     <col min="35" max="38" width="12.5" customWidth="1"/>
-    <col min="39" max="40" width="14.6666666666667" customWidth="1"/>
+    <col min="39" max="40" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="78" spans="1:47">
+    <row r="1" spans="1:47" ht="64">
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
@@ -1930,7 +1310,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" ht="15.6" spans="1:47">
+    <row r="2" spans="1:47" ht="16">
       <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
@@ -2073,7 +1453,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="31.2" spans="1:47">
+    <row r="3" spans="1:47" ht="32">
       <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
@@ -2216,7 +1596,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="31.2" spans="1:47">
+    <row r="4" spans="1:47" ht="32">
       <c r="A4" s="31" t="s">
         <v>3</v>
       </c>
@@ -2359,7 +1739,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="15.6" spans="1:47">
+    <row r="5" spans="1:47" ht="16">
       <c r="A5" s="31" t="s">
         <v>6</v>
       </c>
@@ -2502,7 +1882,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="31.2" spans="1:47">
+    <row r="6" spans="1:47" ht="32">
       <c r="A6" s="31" t="s">
         <v>5</v>
       </c>
@@ -2645,7 +2025,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="15.6" spans="1:47">
+    <row r="7" spans="1:47" ht="16">
       <c r="A7" s="31" t="s">
         <v>4</v>
       </c>
@@ -2788,7 +2168,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" ht="15.6" spans="1:47">
+    <row r="8" spans="1:47" ht="16">
       <c r="A8" s="31" t="s">
         <v>7</v>
       </c>
@@ -2931,7 +2311,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="15.6" spans="1:47">
+    <row r="9" spans="1:47" ht="16">
       <c r="A9" s="31" t="s">
         <v>8</v>
       </c>
@@ -3074,7 +2454,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" ht="15.6" spans="1:47">
+    <row r="10" spans="1:47" ht="16">
       <c r="A10" s="31" t="s">
         <v>9</v>
       </c>
@@ -3217,7 +2597,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="15.6" spans="1:47">
+    <row r="11" spans="1:47" ht="16">
       <c r="A11" s="31" t="s">
         <v>10</v>
       </c>
@@ -3360,7 +2740,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="15.6" spans="1:47">
+    <row r="12" spans="1:47" ht="16">
       <c r="A12" s="31" t="s">
         <v>11</v>
       </c>
@@ -3503,7 +2883,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" ht="15.6" spans="1:47">
+    <row r="13" spans="1:47" ht="16">
       <c r="A13" s="31" t="s">
         <v>12</v>
       </c>
@@ -3646,7 +3026,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="15.6" spans="1:47">
+    <row r="14" spans="1:47" ht="16">
       <c r="A14" s="31" t="s">
         <v>13</v>
       </c>
@@ -3789,7 +3169,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" ht="15.6" spans="1:47">
+    <row r="15" spans="1:47" ht="16">
       <c r="A15" s="31" t="s">
         <v>14</v>
       </c>
@@ -3932,7 +3312,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="31.2" spans="1:47">
+    <row r="16" spans="1:47" ht="32">
       <c r="A16" s="31" t="s">
         <v>15</v>
       </c>
@@ -4075,7 +3455,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="15.6" spans="1:47">
+    <row r="17" spans="1:47" ht="16">
       <c r="A17" s="31" t="s">
         <v>16</v>
       </c>
@@ -4218,7 +3598,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="15.6" spans="1:47">
+    <row r="18" spans="1:47" ht="16">
       <c r="A18" s="31" t="s">
         <v>17</v>
       </c>
@@ -4361,7 +3741,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" ht="15.6" spans="1:47">
+    <row r="19" spans="1:47" ht="16">
       <c r="A19" s="31" t="s">
         <v>18</v>
       </c>
@@ -4504,7 +3884,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" ht="15.6" spans="1:47">
+    <row r="20" spans="1:47" ht="16">
       <c r="A20" s="31" t="s">
         <v>19</v>
       </c>
@@ -4647,7 +4027,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" ht="15.6" spans="1:47">
+    <row r="21" spans="1:47" ht="16">
       <c r="A21" s="31" t="s">
         <v>20</v>
       </c>
@@ -4790,7 +4170,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" ht="15.6" spans="1:47">
+    <row r="22" spans="1:47" ht="16">
       <c r="A22" s="31" t="s">
         <v>21</v>
       </c>
@@ -4933,7 +4313,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" ht="15.6" spans="1:47">
+    <row r="23" spans="1:47" ht="16">
       <c r="A23" s="31" t="s">
         <v>22</v>
       </c>
@@ -5076,7 +4456,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="31.2" spans="1:47">
+    <row r="24" spans="1:47" ht="16">
       <c r="A24" s="31" t="s">
         <v>23</v>
       </c>
@@ -5219,7 +4599,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" ht="15.6" spans="1:47">
+    <row r="25" spans="1:47" ht="16">
       <c r="A25" s="31" t="s">
         <v>24</v>
       </c>
@@ -5362,7 +4742,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" ht="15.6" spans="1:47">
+    <row r="26" spans="1:47" ht="16">
       <c r="A26" s="31" t="s">
         <v>25</v>
       </c>
@@ -5505,7 +4885,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" ht="31.2" spans="1:47">
+    <row r="27" spans="1:47" ht="32">
       <c r="A27" s="31" t="s">
         <v>26</v>
       </c>
@@ -5648,7 +5028,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" ht="31.2" spans="1:47">
+    <row r="28" spans="1:47" ht="32">
       <c r="A28" s="31" t="s">
         <v>27</v>
       </c>
@@ -5791,7 +5171,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" ht="31.2" spans="1:47">
+    <row r="29" spans="1:47" ht="32">
       <c r="A29" s="31" t="s">
         <v>28</v>
       </c>
@@ -5934,7 +5314,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" ht="31.2" spans="1:47">
+    <row r="30" spans="1:47" ht="32">
       <c r="A30" s="31" t="s">
         <v>29</v>
       </c>
@@ -6077,7 +5457,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" ht="15.6" spans="1:47">
+    <row r="31" spans="1:47" ht="16">
       <c r="A31" s="31" t="s">
         <v>30</v>
       </c>
@@ -6220,7 +5600,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" ht="31.2" spans="1:47">
+    <row r="32" spans="1:47" ht="16">
       <c r="A32" s="31" t="s">
         <v>31</v>
       </c>
@@ -6363,7 +5743,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" ht="31.2" spans="1:47">
+    <row r="33" spans="1:47" ht="16">
       <c r="A33" s="31" t="s">
         <v>32</v>
       </c>
@@ -6506,7 +5886,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="15.6" spans="1:47">
+    <row r="34" spans="1:47" ht="16">
       <c r="A34" s="31" t="s">
         <v>33</v>
       </c>
@@ -6649,7 +6029,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" ht="15.6" spans="1:47">
+    <row r="35" spans="1:47" ht="16">
       <c r="A35" s="31" t="s">
         <v>34</v>
       </c>
@@ -6792,7 +6172,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" ht="31.2" spans="1:47">
+    <row r="36" spans="1:47" ht="16">
       <c r="A36" s="31" t="s">
         <v>35</v>
       </c>
@@ -6935,7 +6315,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" ht="15.6" spans="1:47">
+    <row r="37" spans="1:47" ht="16">
       <c r="A37" s="31" t="s">
         <v>36</v>
       </c>
@@ -7078,7 +6458,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" ht="31.2" spans="1:47">
+    <row r="38" spans="1:47" ht="16">
       <c r="A38" s="31" t="s">
         <v>37</v>
       </c>
@@ -7221,7 +6601,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" ht="15.6" spans="1:47">
+    <row r="39" spans="1:47" ht="16">
       <c r="A39" s="31" t="s">
         <v>38</v>
       </c>
@@ -7364,7 +6744,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" ht="15.6" spans="1:47">
+    <row r="40" spans="1:47" ht="16">
       <c r="A40" s="31" t="s">
         <v>39</v>
       </c>
@@ -7507,7 +6887,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" ht="15.6" spans="1:47">
+    <row r="41" spans="1:47" ht="16">
       <c r="A41" s="31" t="s">
         <v>40</v>
       </c>
@@ -7650,7 +7030,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" ht="15.6" spans="1:47">
+    <row r="42" spans="1:47" ht="16">
       <c r="A42" s="31" t="s">
         <v>41</v>
       </c>
@@ -7793,7 +7173,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" ht="15.6" spans="1:47">
+    <row r="43" spans="1:47" ht="16">
       <c r="A43" s="31" t="s">
         <v>42</v>
       </c>
@@ -7936,7 +7316,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" ht="15.6" spans="1:47">
+    <row r="44" spans="1:47" ht="16">
       <c r="A44" s="31" t="s">
         <v>43</v>
       </c>
@@ -8079,7 +7459,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" ht="15.6" spans="1:47">
+    <row r="45" spans="1:47" ht="16">
       <c r="A45" s="31" t="s">
         <v>44</v>
       </c>
@@ -8222,7 +7602,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" ht="31.2" spans="1:47">
+    <row r="46" spans="1:47" ht="32">
       <c r="A46" s="31" t="s">
         <v>45</v>
       </c>
@@ -8365,7 +7745,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="47" ht="31.2" spans="1:47">
+    <row r="47" spans="1:47" ht="32">
       <c r="A47" s="31" t="s">
         <v>46</v>
       </c>
@@ -8508,7 +7888,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:47">
       <c r="A48" s="35"/>
       <c r="B48" s="35"/>
       <c r="C48" s="35"/>
@@ -11744,33 +11124,31 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AO41"/>
-  <sheetFormatPr defaultColWidth="10.6666666666667" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.8333333333333" customWidth="1"/>
-    <col min="2" max="5" width="14.1666666666667" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="5" width="14.1640625" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="11" width="14.1666666666667" customWidth="1"/>
+    <col min="7" max="11" width="14.1640625" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="18" width="14.1666666666667" customWidth="1"/>
+    <col min="14" max="18" width="14.1640625" customWidth="1"/>
     <col min="19" max="19" width="19" customWidth="1"/>
-    <col min="20" max="21" width="9.66666666666667" customWidth="1"/>
-    <col min="22" max="24" width="9.83333333333333" customWidth="1"/>
-    <col min="25" max="25" width="10.6666666666667" customWidth="1"/>
-    <col min="26" max="31" width="9.83333333333333" customWidth="1"/>
-    <col min="32" max="32" width="10.1666666666667" customWidth="1"/>
-    <col min="33" max="35" width="9.83333333333333" customWidth="1"/>
+    <col min="20" max="21" width="9.6640625" customWidth="1"/>
+    <col min="22" max="24" width="9.83203125" customWidth="1"/>
+    <col min="25" max="25" width="10.6640625" customWidth="1"/>
+    <col min="26" max="31" width="9.83203125" customWidth="1"/>
+    <col min="32" max="32" width="10.1640625" customWidth="1"/>
+    <col min="33" max="35" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="78" spans="1:41">
+    <row r="1" spans="1:41" ht="64">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -11895,7 +11273,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" ht="31.2" spans="1:41">
+    <row r="2" spans="1:41" ht="32">
       <c r="A2" s="21" t="s">
         <v>49</v>
       </c>
@@ -12020,7 +11398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="31.2" spans="1:41">
+    <row r="3" spans="1:41" ht="32">
       <c r="A3" s="21" t="s">
         <v>50</v>
       </c>
@@ -12145,7 +11523,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="31.2" spans="1:41">
+    <row r="4" spans="1:41" ht="32">
       <c r="A4" s="21" t="s">
         <v>51</v>
       </c>
@@ -12270,7 +11648,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="31.2" spans="1:41">
+    <row r="5" spans="1:41" ht="16">
       <c r="A5" s="21" t="s">
         <v>52</v>
       </c>
@@ -12395,7 +11773,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="31.2" spans="1:41">
+    <row r="6" spans="1:41" ht="16">
       <c r="A6" s="21" t="s">
         <v>53</v>
       </c>
@@ -12520,7 +11898,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="31.2" spans="1:41">
+    <row r="7" spans="1:41" ht="32">
       <c r="A7" s="21" t="s">
         <v>54</v>
       </c>
@@ -12645,7 +12023,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" ht="31.2" spans="1:41">
+    <row r="8" spans="1:41" ht="32">
       <c r="A8" s="21" t="s">
         <v>55</v>
       </c>
@@ -12770,7 +12148,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="31.2" spans="1:41">
+    <row r="9" spans="1:41" ht="32">
       <c r="A9" s="21" t="s">
         <v>56</v>
       </c>
@@ -12895,7 +12273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" ht="31.2" spans="1:41">
+    <row r="10" spans="1:41" ht="16">
       <c r="A10" s="21" t="s">
         <v>57</v>
       </c>
@@ -13020,7 +12398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="31.2" spans="1:41">
+    <row r="11" spans="1:41" ht="32">
       <c r="A11" s="21" t="s">
         <v>58</v>
       </c>
@@ -13145,7 +12523,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="31.2" spans="1:41">
+    <row r="12" spans="1:41" ht="32">
       <c r="A12" s="21" t="s">
         <v>59</v>
       </c>
@@ -13270,7 +12648,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" ht="31.2" spans="1:41">
+    <row r="13" spans="1:41" ht="32">
       <c r="A13" s="21" t="s">
         <v>60</v>
       </c>
@@ -13395,7 +12773,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="31.2" spans="1:41">
+    <row r="14" spans="1:41" ht="32">
       <c r="A14" s="21" t="s">
         <v>61</v>
       </c>
@@ -13520,7 +12898,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" ht="31.2" spans="1:41">
+    <row r="15" spans="1:41" ht="32">
       <c r="A15" s="21" t="s">
         <v>62</v>
       </c>
@@ -13645,7 +13023,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="31.2" spans="1:41">
+    <row r="16" spans="1:41" ht="32">
       <c r="A16" s="21" t="s">
         <v>63</v>
       </c>
@@ -13770,7 +13148,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="31.2" spans="1:41">
+    <row r="17" spans="1:41" ht="32">
       <c r="A17" s="21" t="s">
         <v>64</v>
       </c>
@@ -13895,7 +13273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" ht="31.2" spans="1:41">
+    <row r="18" spans="1:41" ht="32">
       <c r="A18" s="21" t="s">
         <v>65</v>
       </c>
@@ -14020,7 +13398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" ht="31.2" spans="1:41">
+    <row r="19" spans="1:41" ht="32">
       <c r="A19" s="21" t="s">
         <v>66</v>
       </c>
@@ -14145,7 +13523,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" ht="31.2" spans="1:41">
+    <row r="20" spans="1:41" ht="32">
       <c r="A20" s="21" t="s">
         <v>67</v>
       </c>
@@ -14270,7 +13648,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" ht="31.2" spans="1:41">
+    <row r="21" spans="1:41" ht="32">
       <c r="A21" s="21" t="s">
         <v>68</v>
       </c>
@@ -14395,7 +13773,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" ht="31.2" spans="1:41">
+    <row r="22" spans="1:41" ht="32">
       <c r="A22" s="21" t="s">
         <v>69</v>
       </c>
@@ -14520,7 +13898,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" ht="31.2" spans="1:41">
+    <row r="23" spans="1:41" ht="32">
       <c r="A23" s="21" t="s">
         <v>70</v>
       </c>
@@ -14645,7 +14023,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" ht="31.2" spans="1:41">
+    <row r="24" spans="1:41" ht="32">
       <c r="A24" s="21" t="s">
         <v>71</v>
       </c>
@@ -14770,7 +14148,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" ht="31.2" spans="1:41">
+    <row r="25" spans="1:41" ht="32">
       <c r="A25" s="21" t="s">
         <v>72</v>
       </c>
@@ -14895,7 +14273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" ht="31.2" spans="1:41">
+    <row r="26" spans="1:41" ht="32">
       <c r="A26" s="21" t="s">
         <v>73</v>
       </c>
@@ -15020,7 +14398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" ht="31.2" spans="1:41">
+    <row r="27" spans="1:41" ht="32">
       <c r="A27" s="21" t="s">
         <v>74</v>
       </c>
@@ -15145,7 +14523,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" ht="31.2" spans="1:41">
+    <row r="28" spans="1:41" ht="32">
       <c r="A28" s="21" t="s">
         <v>75</v>
       </c>
@@ -15270,7 +14648,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" ht="31.2" spans="1:41">
+    <row r="29" spans="1:41" ht="32">
       <c r="A29" s="21" t="s">
         <v>76</v>
       </c>
@@ -15395,7 +14773,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" ht="31.2" spans="1:41">
+    <row r="30" spans="1:41" ht="32">
       <c r="A30" s="21" t="s">
         <v>77</v>
       </c>
@@ -15520,7 +14898,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" ht="31.2" spans="1:41">
+    <row r="31" spans="1:41" ht="16">
       <c r="A31" s="21" t="s">
         <v>78</v>
       </c>
@@ -15645,7 +15023,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" ht="31.2" spans="1:41">
+    <row r="32" spans="1:41" ht="32">
       <c r="A32" s="21" t="s">
         <v>79</v>
       </c>
@@ -15768,7 +15146,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" ht="31.2" spans="1:41">
+    <row r="33" spans="1:41" ht="32">
       <c r="A33" s="21" t="s">
         <v>80</v>
       </c>
@@ -15893,7 +15271,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="31.2" spans="1:41">
+    <row r="34" spans="1:41" ht="32">
       <c r="A34" s="21" t="s">
         <v>81</v>
       </c>
@@ -16018,7 +15396,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" ht="31.2" spans="1:41">
+    <row r="35" spans="1:41" ht="32">
       <c r="A35" s="21" t="s">
         <v>82</v>
       </c>
@@ -16143,7 +15521,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" ht="31.2" spans="1:41">
+    <row r="36" spans="1:41" ht="32">
       <c r="A36" s="21" t="s">
         <v>83</v>
       </c>
@@ -16268,7 +15646,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" ht="31.2" spans="1:41">
+    <row r="37" spans="1:41" ht="32">
       <c r="A37" s="21" t="s">
         <v>84</v>
       </c>
@@ -16393,7 +15771,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" ht="31.2" spans="1:41">
+    <row r="38" spans="1:41" ht="32">
       <c r="A38" s="21" t="s">
         <v>85</v>
       </c>
@@ -16518,7 +15896,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" ht="31.2" spans="1:41">
+    <row r="39" spans="1:41" ht="32">
       <c r="A39" s="21" t="s">
         <v>86</v>
       </c>
@@ -16643,7 +16021,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" ht="31.2" spans="1:41">
+    <row r="40" spans="1:41" ht="32">
       <c r="A40" s="21" t="s">
         <v>87</v>
       </c>
@@ -16768,7 +16146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" ht="31.2" spans="1:41">
+    <row r="41" spans="1:41" ht="32">
       <c r="A41" s="21" t="s">
         <v>88</v>
       </c>
@@ -16895,25 +16273,23 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:Y25"/>
-  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Z26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="10" max="10" width="8.66666666666667" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
     <col min="11" max="12" width="10" customWidth="1"/>
-    <col min="13" max="13" width="9.33333333333333" customWidth="1"/>
-    <col min="14" max="15" width="10.6666666666667" customWidth="1"/>
-    <col min="16" max="21" width="9.66666666666667" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" customWidth="1"/>
+    <col min="14" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="21" width="9.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="63.15" spans="1:25">
+    <row r="1" spans="1:26" ht="49" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16989,8 +16365,11 @@
       <c r="Y1" s="16" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="2" ht="47.55" spans="1:25">
+      <c r="Z1" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" ht="33" thickBot="1">
       <c r="A2" s="10" t="s">
         <v>89</v>
       </c>
@@ -17066,8 +16445,11 @@
       <c r="Y2" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="3" ht="47.55" spans="1:25">
+      <c r="Z2" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="33" thickBot="1">
       <c r="A3" s="10" t="s">
         <v>90</v>
       </c>
@@ -17143,8 +16525,11 @@
       <c r="Y3" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" ht="47.55" spans="1:25">
+      <c r="Z3" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="49" thickBot="1">
       <c r="A4" s="10" t="s">
         <v>91</v>
       </c>
@@ -17220,8 +16605,11 @@
       <c r="Y4" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" ht="47.55" spans="1:25">
+      <c r="Z4" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="33" thickBot="1">
       <c r="A5" s="10" t="s">
         <v>92</v>
       </c>
@@ -17297,8 +16685,11 @@
       <c r="Y5" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" ht="47.55" spans="1:25">
+      <c r="Z5" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="33" thickBot="1">
       <c r="A6" s="10" t="s">
         <v>93</v>
       </c>
@@ -17374,8 +16765,11 @@
       <c r="Y6" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="7" ht="47.55" spans="1:25">
+      <c r="Z6" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="33" thickBot="1">
       <c r="A7" s="10" t="s">
         <v>94</v>
       </c>
@@ -17451,8 +16845,11 @@
       <c r="Y7" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" ht="47.55" spans="1:25">
+      <c r="Z7" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="33" thickBot="1">
       <c r="A8" s="10" t="s">
         <v>95</v>
       </c>
@@ -17528,8 +16925,11 @@
       <c r="Y8" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" ht="47.55" spans="1:25">
+      <c r="Z8" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="33" thickBot="1">
       <c r="A9" s="10" t="s">
         <v>96</v>
       </c>
@@ -17605,8 +17005,11 @@
       <c r="Y9" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" ht="47.55" spans="1:25">
+      <c r="Z9" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="49" thickBot="1">
       <c r="A10" s="10" t="s">
         <v>91</v>
       </c>
@@ -17682,8 +17085,11 @@
       <c r="Y10" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="11" ht="55" customHeight="1" spans="1:25">
+      <c r="Z10" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="55" customHeight="1" thickBot="1">
       <c r="A11" s="10" t="s">
         <v>97</v>
       </c>
@@ -17759,8 +17165,11 @@
       <c r="Y11" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" ht="61" customHeight="1" spans="1:25">
+      <c r="Z11" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="61" customHeight="1" thickBot="1">
       <c r="A12" s="10" t="s">
         <v>98</v>
       </c>
@@ -17836,8 +17245,11 @@
       <c r="Y12" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:25">
+      <c r="Z12" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="36" customHeight="1" thickBot="1">
       <c r="A13" s="10" t="s">
         <v>99</v>
       </c>
@@ -17913,8 +17325,11 @@
       <c r="Y13" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="14" ht="47.55" spans="1:25">
+      <c r="Z13" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="33" thickBot="1">
       <c r="A14" s="10" t="s">
         <v>100</v>
       </c>
@@ -17990,8 +17405,11 @@
       <c r="Y14" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="15" ht="47.55" spans="1:25">
+      <c r="Z14" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="33" thickBot="1">
       <c r="A15" s="10" t="s">
         <v>101</v>
       </c>
@@ -18067,8 +17485,11 @@
       <c r="Y15" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" ht="63.15" spans="1:25">
+      <c r="Z15" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="49" thickBot="1">
       <c r="A16" s="10" t="s">
         <v>102</v>
       </c>
@@ -18144,8 +17565,11 @@
       <c r="Y16" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="17" ht="47.55" spans="1:25">
+      <c r="Z16" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="49" thickBot="1">
       <c r="A17" s="10" t="s">
         <v>103</v>
       </c>
@@ -18221,8 +17645,11 @@
       <c r="Y17" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="18" ht="47.55" spans="1:25">
+      <c r="Z17" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="49" thickBot="1">
       <c r="A18" s="10" t="s">
         <v>104</v>
       </c>
@@ -18298,8 +17725,11 @@
       <c r="Y18" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="19" ht="47.55" spans="1:25">
+      <c r="Z18" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="49" thickBot="1">
       <c r="A19" s="10" t="s">
         <v>105</v>
       </c>
@@ -18375,8 +17805,11 @@
       <c r="Y19" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="20" ht="63.15" spans="1:25">
+      <c r="Z19" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="49" thickBot="1">
       <c r="A20" s="10" t="s">
         <v>106</v>
       </c>
@@ -18452,8 +17885,11 @@
       <c r="Y20" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="21" ht="63.15" spans="1:25">
+      <c r="Z20" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="49" thickBot="1">
       <c r="A21" s="10" t="s">
         <v>107</v>
       </c>
@@ -18529,8 +17965,11 @@
       <c r="Y21" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="22" ht="63.15" spans="1:25">
+      <c r="Z21" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="49" thickBot="1">
       <c r="A22" s="10" t="s">
         <v>108</v>
       </c>
@@ -18606,8 +18045,11 @@
       <c r="Y22" s="12" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" ht="47.55" spans="1:25">
+      <c r="Z22" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="33" thickBot="1">
       <c r="A23" s="9" t="s">
         <v>109</v>
       </c>
@@ -18683,8 +18125,11 @@
       <c r="Y23" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" ht="63.15" spans="1:25">
+      <c r="Z23" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="49" thickBot="1">
       <c r="A24" s="9" t="s">
         <v>110</v>
       </c>
@@ -18760,8 +18205,11 @@
       <c r="Y24" s="12" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" ht="47.55" spans="1:25">
+      <c r="Z24" s="12" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="33" thickBot="1">
       <c r="A25" s="9" t="s">
         <v>111</v>
       </c>
@@ -18837,23 +18285,104 @@
       <c r="Y25" s="12" t="s">
         <v>48</v>
       </c>
+      <c r="Z25" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="33" thickBot="1">
+      <c r="A26" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="L26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="O26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="P26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="R26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="T26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="U26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="V26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="W26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="X26" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y26" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z26" s="12" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="9.16666666666667" customWidth="1"/>
+    <col min="1" max="6" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36.75" customHeight="1" spans="1:6">
+    <row r="1" spans="1:6" ht="36.75" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -18873,7 +18402,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" ht="36.75" customHeight="1" spans="1:6">
+    <row r="2" spans="1:6" ht="36.75" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>112</v>
       </c>
@@ -18893,7 +18422,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="36.75" customHeight="1" spans="1:6">
+    <row r="3" spans="1:6" ht="36.75" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>113</v>
       </c>
@@ -18913,7 +18442,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="36.75" customHeight="1" spans="1:6">
+    <row r="4" spans="1:6" ht="36.75" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>114</v>
       </c>
@@ -18933,7 +18462,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="36.75" customHeight="1" spans="1:6">
+    <row r="5" spans="1:6" ht="36.75" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>115</v>
       </c>
@@ -18953,7 +18482,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="36.75" customHeight="1" spans="1:6">
+    <row r="6" spans="1:6" ht="36.75" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>116</v>
       </c>
@@ -18975,17 +18504,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="47.55" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -19005,7 +18532,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" ht="47.55" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>117</v>
       </c>
@@ -19025,7 +18552,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="47.55" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>118</v>
       </c>
@@ -19045,7 +18572,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="47.55" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>119</v>
       </c>
@@ -19065,7 +18592,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="47.55" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>120</v>
       </c>
@@ -19085,7 +18612,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="47.55" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>121</v>
       </c>
@@ -19107,17 +18634,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9.16666666666667" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="31.95" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -19137,7 +18662,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="2" ht="31.95" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>122</v>
       </c>
@@ -19157,7 +18682,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="31.95" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>123</v>
       </c>
@@ -19177,7 +18702,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="31.95" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>124</v>
       </c>
@@ -19197,7 +18722,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="31.95" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>125</v>
       </c>
@@ -19217,7 +18742,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="31.95" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>126</v>
       </c>
@@ -19239,17 +18764,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="31.95" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -19269,7 +18792,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="2" ht="31.95" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>127</v>
       </c>
@@ -19289,7 +18812,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="31.95" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>128</v>
       </c>
@@ -19309,7 +18832,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="31.95" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>129</v>
       </c>
@@ -19329,7 +18852,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="31.95" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>130</v>
       </c>
@@ -19349,7 +18872,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="31.95" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>131</v>
       </c>
@@ -19371,17 +18894,15 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="31.95" spans="1:6">
+    <row r="1" spans="1:6" ht="32">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -19401,7 +18922,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="2" ht="31.95" spans="1:6">
+    <row r="2" spans="1:6" ht="32">
       <c r="A2" s="6" t="s">
         <v>132</v>
       </c>
@@ -19421,7 +18942,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" ht="31.95" spans="1:6">
+    <row r="3" spans="1:6" ht="32">
       <c r="A3" s="6" t="s">
         <v>133</v>
       </c>
@@ -19441,7 +18962,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" ht="31.95" spans="1:6">
+    <row r="4" spans="1:6" ht="32">
       <c r="A4" s="6" t="s">
         <v>134</v>
       </c>
@@ -19461,7 +18982,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" ht="31.95" spans="1:6">
+    <row r="5" spans="1:6" ht="32">
       <c r="A5" s="6" t="s">
         <v>135</v>
       </c>
@@ -19481,7 +19002,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" ht="31.95" spans="1:6">
+    <row r="6" spans="1:6" ht="32">
       <c r="A6" s="6" t="s">
         <v>136</v>
       </c>
@@ -19503,20 +19024,18 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="78.75" spans="1:20">
+    <row r="1" spans="1:20" ht="80">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19578,7 +19097,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" ht="31.95" spans="1:20">
+    <row r="2" spans="1:20" ht="32">
       <c r="A2" s="1" t="s">
         <v>137</v>
       </c>
@@ -19640,7 +19159,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" ht="31.95" spans="1:20">
+    <row r="3" spans="1:20" ht="32">
       <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
@@ -19702,7 +19221,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" ht="31.95" spans="1:20">
+    <row r="4" spans="1:20" ht="32">
       <c r="A4" s="1" t="s">
         <v>139</v>
       </c>
@@ -19764,7 +19283,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" ht="31.95" spans="1:20">
+    <row r="5" spans="1:20" ht="32">
       <c r="A5" s="1" t="s">
         <v>140</v>
       </c>
@@ -19826,7 +19345,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="31.95" spans="1:20">
+    <row r="6" spans="1:20" ht="32">
       <c r="A6" s="1" t="s">
         <v>141</v>
       </c>
@@ -19888,7 +19407,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="31.95" spans="1:20">
+    <row r="7" spans="1:20" ht="32">
       <c r="A7" s="1" t="s">
         <v>142</v>
       </c>
@@ -19950,7 +19469,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" ht="31.95" spans="1:20">
+    <row r="8" spans="1:20" ht="32">
       <c r="A8" s="1" t="s">
         <v>143</v>
       </c>
@@ -20012,7 +19531,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="31.95" spans="1:20">
+    <row r="9" spans="1:20" ht="32">
       <c r="A9" s="1" t="s">
         <v>144</v>
       </c>
@@ -20074,7 +19593,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" ht="31.95" spans="1:20">
+    <row r="10" spans="1:20" ht="32">
       <c r="A10" s="1" t="s">
         <v>145</v>
       </c>
@@ -20136,7 +19655,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" ht="31.95" spans="1:20">
+    <row r="11" spans="1:20" ht="32">
       <c r="A11" s="1" t="s">
         <v>146</v>
       </c>
@@ -20198,7 +19717,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" ht="31.95" spans="1:20">
+    <row r="12" spans="1:20" ht="32">
       <c r="A12" s="1" t="s">
         <v>147</v>
       </c>
@@ -20260,7 +19779,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" ht="31.95" spans="1:20">
+    <row r="13" spans="1:20" ht="32">
       <c r="A13" s="1" t="s">
         <v>148</v>
       </c>
@@ -20322,7 +19841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" ht="47.55" spans="1:20">
+    <row r="14" spans="1:20" ht="32">
       <c r="A14" s="1" t="s">
         <v>149</v>
       </c>
@@ -20384,7 +19903,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" ht="47.55" spans="1:20">
+    <row r="15" spans="1:20" ht="48">
       <c r="A15" s="1" t="s">
         <v>150</v>
       </c>
@@ -20446,7 +19965,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" ht="31.95" spans="1:20">
+    <row r="16" spans="1:20" ht="32">
       <c r="A16" s="1" t="s">
         <v>151</v>
       </c>
@@ -20508,7 +20027,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" ht="31.95" spans="1:20">
+    <row r="17" spans="1:20" ht="32">
       <c r="A17" s="1" t="s">
         <v>152</v>
       </c>
@@ -20570,7 +20089,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" ht="31.95" spans="1:20">
+    <row r="18" spans="1:20" ht="32">
       <c r="A18" s="1" t="s">
         <v>153</v>
       </c>
@@ -20632,7 +20151,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" ht="31.95" spans="1:20">
+    <row r="19" spans="1:20" ht="32">
       <c r="A19" s="1" t="s">
         <v>154</v>
       </c>
@@ -20694,7 +20213,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" ht="31.95" spans="1:20">
+    <row r="20" spans="1:20" ht="32">
       <c r="A20" s="1" t="s">
         <v>155</v>
       </c>
@@ -20758,6 +20277,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/dbm-ui/backend/ticket/exclusive_ticket.xlsx
+++ b/dbm-ui/backend/ticket/exclusive_ticket.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevnzheng/Projects/blueking-dbm/dbm-ui/backend/ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C424F28-81CB-1D43-A86A-861F97018F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE2480C-59E1-C94A-BD74-0A9944B8643C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4360" yWindow="680" windowWidth="30200" windowHeight="20060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16446,7 +16446,7 @@
         <v>48</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="33" thickBot="1">
@@ -16526,7 +16526,7 @@
         <v>48</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="49" thickBot="1">
@@ -16606,7 +16606,7 @@
         <v>48</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="33" thickBot="1">
@@ -16766,7 +16766,7 @@
         <v>48</v>
       </c>
       <c r="Z6" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="33" thickBot="1">
@@ -16846,7 +16846,7 @@
         <v>48</v>
       </c>
       <c r="Z7" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="33" thickBot="1">
@@ -16926,7 +16926,7 @@
         <v>48</v>
       </c>
       <c r="Z8" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="33" thickBot="1">
@@ -17006,7 +17006,7 @@
         <v>48</v>
       </c>
       <c r="Z9" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="49" thickBot="1">
@@ -17086,7 +17086,7 @@
         <v>48</v>
       </c>
       <c r="Z10" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="55" customHeight="1" thickBot="1">
@@ -17166,7 +17166,7 @@
         <v>48</v>
       </c>
       <c r="Z11" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="61" customHeight="1" thickBot="1">
@@ -17246,7 +17246,7 @@
         <v>48</v>
       </c>
       <c r="Z12" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="36" customHeight="1" thickBot="1">
@@ -17326,7 +17326,7 @@
         <v>48</v>
       </c>
       <c r="Z13" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="33" thickBot="1">
@@ -17406,7 +17406,7 @@
         <v>48</v>
       </c>
       <c r="Z14" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="33" thickBot="1">
@@ -17486,7 +17486,7 @@
         <v>48</v>
       </c>
       <c r="Z15" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="49" thickBot="1">
@@ -17566,7 +17566,7 @@
         <v>48</v>
       </c>
       <c r="Z16" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="49" thickBot="1">
@@ -17646,7 +17646,7 @@
         <v>48</v>
       </c>
       <c r="Z17" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="49" thickBot="1">
@@ -17806,7 +17806,7 @@
         <v>48</v>
       </c>
       <c r="Z19" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="49" thickBot="1">
@@ -17966,7 +17966,7 @@
         <v>48</v>
       </c>
       <c r="Z21" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="49" thickBot="1">
@@ -18046,7 +18046,7 @@
         <v>48</v>
       </c>
       <c r="Z22" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="33" thickBot="1">
@@ -18286,7 +18286,7 @@
         <v>48</v>
       </c>
       <c r="Z25" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="33" thickBot="1">
@@ -18294,67 +18294,67 @@
         <v>156</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>48</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R26" s="12" t="s">
         <v>48</v>
       </c>
       <c r="S26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T26" s="12" t="s">
         <v>48</v>
       </c>
       <c r="U26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W26" s="12" t="s">
         <v>47</v>
@@ -18363,7 +18363,7 @@
         <v>47</v>
       </c>
       <c r="Y26" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z26" s="12" t="s">
         <v>48</v>
